--- a/workspaces/btc_daily_14days/ma/ma_cross_50_200.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_50_200.xlsx
@@ -575,46 +575,46 @@
         <v>55</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.584347411118237</v>
+        <v>-1.578020291706409</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-3.196802577539394</v>
+        <v>-3.185342382619588</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-7.231049544176742</v>
+        <v>-7.205724392815135</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-7.102756925592089</v>
+        <v>-7.07737793058395</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.463588228900313</v>
+        <v>-9.43081210496775</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.62994928052196</v>
+        <v>-14.57965879091611</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.89752492272107</v>
+        <v>-12.85339807131329</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-4.261162010223096</v>
+        <v>-4.246808118276533</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.142478337395239</v>
+        <v>1.138633976558914</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.113193113981993</v>
+        <v>2.105936363835113</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.377219952256674</v>
+        <v>7.352183756663472</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.589891275757672</v>
+        <v>5.571302934639128</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.345409155170984</v>
+        <v>3.334919341559441</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.772774382107187</v>
+        <v>1.767265764394409</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>119</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4472926123473613</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.164214287847422</v>
+        <v>-1.159289559446989</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.55974730467242</v>
+        <v>-1.552966923984677</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2519946081483084</v>
+        <v>0.2529766462786895</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.236774467313396</v>
+        <v>2.230384815565998</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.059352572534841</v>
+        <v>5.043508664360573</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.659274378181692</v>
+        <v>6.637440737677601</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.82585214232197</v>
+        <v>2.816227006236829</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.923480727490521</v>
+        <v>1.916741248982731</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.441416143749635</v>
+        <v>4.425724515616452</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.552374637593154</v>
+        <v>2.542952859084707</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.272767321303583</v>
+        <v>4.257894400209111</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.851686854526505</v>
+        <v>3.838948020675694</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.319864414627702</v>
+        <v>8.291329935516188</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>119</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.170427226008513</v>
+        <v>7.145803463044118</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.60371838982629</v>
+        <v>10.56669477905758</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.21139516753826</v>
+        <v>10.17633771414661</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.18541279982191</v>
+        <v>11.14718491493003</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.125765674291898</v>
+        <v>8.097801658685931</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.267247614018125</v>
+        <v>9.235246345886708</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.86859646353358</v>
+        <v>10.83020642801704</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.92976995662622</v>
+        <v>12.88321701894521</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>12.030128393359</v>
+        <v>11.9866410796641</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.39373736678164</v>
+        <v>15.33767138567944</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>16.87815045089849</v>
+        <v>16.81664868652121</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.23127322350489</v>
+        <v>15.17605757459907</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.12691274869795</v>
+        <v>13.0800181317346</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>10.0084789867861</v>
+        <v>9.972002204424129</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>216</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.660104986876746</v>
+        <v>-6.63431794814425</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.810998623928555</v>
+        <v>-7.781319792271773</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.818779973496795</v>
+        <v>-6.792230600574428</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.520167891704531</v>
+        <v>-2.50980153400107</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.913924667361236</v>
+        <v>-4.894827845702274</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.544776066712238</v>
+        <v>-5.52334334041926</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.094675456215278</v>
+        <v>-6.072042314224134</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.244390747012972</v>
+        <v>-4.229918455477474</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.522284114157422</v>
+        <v>-1.518280063611613</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5175384202031665</v>
+        <v>-0.5183400811284784</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.57991146104586</v>
+        <v>-2.573134731803322</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.546460666512353</v>
+        <v>-2.539198120241252</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.040580602003637</v>
+        <v>-2.034149413243469</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.648880269344154</v>
+        <v>-3.636774639646823</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>271</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.643093045103754</v>
+        <v>0.6425763524973931</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2306908833152335</v>
+        <v>-0.2278608414451426</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.3645860196781</v>
+        <v>-1.356547175742314</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6121584115927234</v>
+        <v>0.6111352974755633</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6658705361359836</v>
+        <v>-0.661436725830221</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3683256691277066</v>
+        <v>-0.3650462370441403</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.671332420175716</v>
+        <v>-2.659389290738389</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.660217718783862</v>
+        <v>-1.654221239313813</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.091292996034753</v>
+        <v>-2.084304562321826</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.943447315743704</v>
+        <v>-2.934304402348687</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.039156739483474</v>
+        <v>-2.033570797035104</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.59780790148239</v>
+        <v>-4.580901557609508</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.281194045891638</v>
+        <v>-4.264462741008494</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.031604963121296</v>
+        <v>-4.016028432184747</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>205</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.249535881185587</v>
+        <v>-2.237289256278842</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.790432974938277</v>
+        <v>-6.75800821249377</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.140778272143578</v>
+        <v>-9.096894881232984</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.525059573437169</v>
+        <v>-8.485666961047215</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.067457793946552</v>
+        <v>-9.024988066982907</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.306852680109827</v>
+        <v>-7.272223107672936</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-10.32719884102011</v>
+        <v>-10.27931065074146</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.77583549429239</v>
+        <v>-11.72393626275208</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-14.28624490548414</v>
+        <v>-14.22395723389253</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-17.10014711148885</v>
+        <v>-17.02664166850008</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-20.24804705391269</v>
+        <v>-20.16067960046536</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-20.22180669531895</v>
+        <v>-20.13275843002385</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-19.1823451858579</v>
+        <v>-19.09671088611865</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-17.46794809614157</v>
+        <v>-17.39016217352216</v>
       </c>
     </row>
     <row r="12">
@@ -884,49 +884,49 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.285456152151831</v>
+        <v>3.450298065817087</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>6.976025516548731</v>
+        <v>7.355815083793566</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.373804022858536</v>
+        <v>8.816575813135557</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.776128633320276</v>
+        <v>9.274296678435796</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.03813274961219</v>
+        <v>10.60410350194365</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.094087116195183</v>
+        <v>8.544245765328895</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.789247794017719</v>
+        <v>7.145087043914792</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.59744030401103</v>
+        <v>5.90802543024153</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.819443705725604</v>
+        <v>6.144672820891252</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.786370798072859</v>
+        <v>6.116588182838136</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.881356043074724</v>
+        <v>5.141618838004568</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.219478045381116</v>
+        <v>4.410024045682768</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.623959871233836</v>
+        <v>3.762685276541653</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>3.848926389502815</v>
+        <v>4.013255069206409</v>
       </c>
     </row>
     <row r="13">
@@ -936,49 +936,49 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.008289805358487</v>
+        <v>-1.015855559526692</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.34053262128122</v>
+        <v>1.344281190649376</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.93576292458561</v>
+        <v>1.94078990778457</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.08581803739102867</v>
+        <v>0.0842759958493815</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.022644347071434</v>
+        <v>2.030134263130847</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.310185294687976</v>
+        <v>3.324060057224436</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.205649597217679</v>
+        <v>5.227552365251</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.748367188535298</v>
+        <v>3.76516171825304</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.172515817204371</v>
+        <v>5.196516772909021</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>8.777836176731128</v>
+        <v>8.820356076289713</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.592884832611567</v>
+        <v>6.623182156999846</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>11.08271353451157</v>
+        <v>11.13280641091517</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>13.63275595326953</v>
+        <v>13.69416134754027</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>11.69187868773206</v>
+        <v>11.7446515626749</v>
       </c>
     </row>
     <row r="14">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.3197</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3899~3912</t>
-        </is>
+      <c r="B6" t="n">
+        <v>3899</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.2928602482971883</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.2799</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3844~3857</t>
-        </is>
+      <c r="B7" t="n">
+        <v>3844</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.3196288304252306</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.2402</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>3725~3738</t>
-        </is>
+      <c r="B8" t="n">
+        <v>3725</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.3155504438349652</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.2004</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3606~3619</t>
-        </is>
+      <c r="B9" t="n">
+        <v>3606</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.09014830592984424</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.1607</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>3390~3403</t>
-        </is>
+      <c r="B10" t="n">
+        <v>3390</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.5186098725611146</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.1209</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>3119~3132</t>
-        </is>
+      <c r="B11" t="n">
+        <v>3119</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>0.5078388189981951</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.08116</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2914~2927</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2914</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>0.7009586732987358</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.04141</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2727~2728</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2727</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>0.5124267824293156</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.001654</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2526~2526</t>
-        </is>
+      <c r="B14" t="n">
+        <v>2526</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>0.634035947406808</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; 0.0381</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2345~2345</t>
-        </is>
+      <c r="B15" t="n">
+        <v>2345</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>0.9820414239264821</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; 0.07786</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2104~2104</t>
-        </is>
+      <c r="B16" t="n">
+        <v>2104</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>0.9761434288394568</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; 0.1176</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1754~1754</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1754</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>0.8132891598356338</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; 0.1574</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1492~1492</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1492</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>0.9247922427927051</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; 0.1971</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1318~1318</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1318</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.072570784494118</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; 0.2369</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1134~1134</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1134</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>0.8575316974267153</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 0.2766</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>923~923</t>
-        </is>
+      <c r="B21" t="n">
+        <v>923</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>-0.05573517828148056</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.3164</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>740~740</t>
-        </is>
+      <c r="B22" t="n">
+        <v>740</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>1.560615733844081</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.3561</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>605~605</t>
-        </is>
+      <c r="B23" t="n">
+        <v>605</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.556148456649531</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.3959</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>549~549</t>
-        </is>
+      <c r="B24" t="n">
+        <v>549</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>2.33351978543665</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.4356</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>509~509</t>
-        </is>
+      <c r="B25" t="n">
+        <v>509</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.712848516725195</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.4754</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>469~469</t>
-        </is>
+      <c r="B26" t="n">
+        <v>469</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.517222660600261</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.5152</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>408~408</t>
-        </is>
+      <c r="B27" t="n">
+        <v>408</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>1.428130307241005</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.5549</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>357~357</t>
-        </is>
+      <c r="B28" t="n">
+        <v>357</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.4477381503782638</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.5947</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>317~317</t>
-        </is>
+      <c r="B29" t="n">
+        <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-2.020252200336159</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.6344</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>257~257</t>
-        </is>
+      <c r="B30" t="n">
+        <v>257</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-4.244411082855891</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.6742</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>182~182</t>
-        </is>
+      <c r="B31" t="n">
+        <v>182</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-0.295636122407771</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.7139</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>145~145</t>
-        </is>
+      <c r="B32" t="n">
+        <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.6100099556520888</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.7537</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>128~128</t>
-        </is>
+      <c r="B33" t="n">
+        <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-0.9309383202099752</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.7934</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>111~111</t>
-        </is>
+      <c r="B34" t="n">
+        <v>111</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-0.2411860679577273</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.8332</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>80~80</t>
-        </is>
+      <c r="B35" t="n">
+        <v>80</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-4.993438320209975</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.3197</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>80~80</t>
-        </is>
+      <c r="B6" t="n">
+        <v>80</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>-8.743438320209975</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.2799</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>135~135</t>
-        </is>
+      <c r="B7" t="n">
+        <v>135</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>-5.826771653543311</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.2402</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>254~254</t>
-        </is>
+      <c r="B8" t="n">
+        <v>254</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>-2.887139107611546</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.2004</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>373~373</t>
-        </is>
+      <c r="B9" t="n">
+        <v>373</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.3215750846157661</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.1607</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>589~589</t>
-        </is>
+      <c r="B10" t="n">
+        <v>589</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-2.238769389819488</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.1209</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>860~860</t>
-        </is>
+      <c r="B11" t="n">
+        <v>860</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-1.330647622535551</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.08116</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1065~1065</t>
-        </is>
+      <c r="B12" t="n">
+        <v>1065</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-1.507522827252231</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.04141</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1252~1264</t>
-        </is>
+      <c r="B13" t="n">
+        <v>1252</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-0.7529319910960552</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.001654</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1453~1466</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1453</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-0.7881177199371194</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; 0.0381</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1634~1647</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1634</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.127318101630742</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; 0.07786</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1875~1888</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1875</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.8514891676676015</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; 0.1176</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2225~2238</t>
-        </is>
+      <c r="B17" t="n">
+        <v>2225</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.4380317071626152</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; 0.1574</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2487~2500</t>
-        </is>
+      <c r="B18" t="n">
+        <v>2487</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.3734383202099778</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; 0.1971</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2661~2674</t>
-        </is>
+      <c r="B19" t="n">
+        <v>2661</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.36180032469764</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; 0.2369</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2845~2858</t>
-        </is>
+      <c r="B20" t="n">
+        <v>2845</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.1841311123723202</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 0.2766</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>3056~3069</t>
-        </is>
+      <c r="B21" t="n">
+        <v>3056</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.1621498192491302</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.3164</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>3239~3252</t>
-        </is>
+      <c r="B22" t="n">
+        <v>3239</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.2179155649824196</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.3561</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>3374~3387</t>
-        </is>
+      <c r="B23" t="n">
+        <v>3374</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>-0.1462283999265424</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.3959</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>3430~3443</t>
-        </is>
+      <c r="B24" t="n">
+        <v>3430</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>-0.2424943759752907</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.4356</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>3470~3483</t>
-        </is>
+      <c r="B25" t="n">
+        <v>3470</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>-0.2683450098453548</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.4754</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>3510~3523</t>
-        </is>
+      <c r="B26" t="n">
+        <v>3510</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>-0.2084539319045504</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.5152</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>3571~3584</t>
-        </is>
+      <c r="B27" t="n">
+        <v>3571</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>-0.03808117735283645</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.5549</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>3622~3635</t>
-        </is>
+      <c r="B28" t="n">
+        <v>3622</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.07877626025770468</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.5947</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>3662~3675</t>
-        </is>
+      <c r="B29" t="n">
+        <v>3662</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>0.2956773260485264</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.6344</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>3722~3735</t>
-        </is>
+      <c r="B30" t="n">
+        <v>3722</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>0.4115148257070231</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.6742</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>3797~3810</t>
-        </is>
+      <c r="B31" t="n">
+        <v>3797</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>0.1312335958005235</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.7139</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>3834~3847</t>
-        </is>
+      <c r="B32" t="n">
+        <v>3834</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>0.09299266497328773</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.7537</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>3851~3864</t>
-        </is>
+      <c r="B33" t="n">
+        <v>3851</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>0.146313232585058</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.7934</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>3868~3881</t>
-        </is>
+      <c r="B34" t="n">
+        <v>3868</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>0.1218670134669111</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.8332</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>3899~3912</t>
-        </is>
+      <c r="B35" t="n">
+        <v>3899</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>0.2161731317327664</v>

--- a/workspaces/btc_daily_14days/ma/ma_cross_50_200.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_50_200.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-50-200 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-50-200 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -575,98 +575,98 @@
         <v>55</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.578020291706409</v>
+        <v>-1.565545098164655</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-3.185342382619588</v>
+        <v>-3.172478507371096</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-7.205724392815135</v>
+        <v>-7.192762777331076</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-7.07737793058395</v>
+        <v>-7.064440206375764</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.43081210496775</v>
+        <v>-9.417740146168192</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.57965879091611</v>
+        <v>-14.5666530957199</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.85339807131329</v>
+        <v>-12.84036351598883</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-4.246808118276533</v>
+        <v>-4.233650831685473</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.138633976558914</v>
+        <v>1.151814733033213</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.105936363835113</v>
+        <v>2.119327155593417</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.352183756663472</v>
+        <v>7.365631320344711</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.571302934639128</v>
+        <v>5.584748463042942</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.334919341559441</v>
+        <v>3.348471805373386</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.767265764394409</v>
+        <v>1.756836128697081</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.2601</t>
+          <t>X ≈ -0.26</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>119</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.4472926123473613</v>
+        <v>0.4597674255555901</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.159289559446989</v>
+        <v>-1.14642620850065</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.552966923984677</v>
+        <v>-1.540003228768754</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2529766462786895</v>
+        <v>0.2659174647400278</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.230384815565998</v>
+        <v>2.243462224334529</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.043508664360573</v>
+        <v>5.056523525357136</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.637440737677601</v>
+        <v>6.650483329853706</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.816227006236829</v>
+        <v>2.829386152284087</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.916741248982731</v>
+        <v>1.929921465267377</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.425724515616452</v>
+        <v>4.439115334427591</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.542952859084707</v>
+        <v>2.556399002451791</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.257894400209111</v>
+        <v>4.271339459757094</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.838948020675694</v>
+        <v>3.852500363652766</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.291329935516188</v>
+        <v>8.28090029981842</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>119</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.145803463044118</v>
+        <v>7.15828183393883</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.56669477905758</v>
+        <v>10.57956577421308</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.17633771414661</v>
+        <v>10.18930833678858</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.14718491493003</v>
+        <v>11.1601315504719</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.097801658685931</v>
+        <v>8.110880999961225</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.235246345886708</v>
+        <v>9.248262111611339</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.83020642801704</v>
+        <v>10.84324992871511</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.88321701894521</v>
+        <v>12.89637944208875</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.9866410796641</v>
+        <v>11.99982398847035</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.33767138567944</v>
+        <v>15.3510647016856</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>16.81664868652121</v>
+        <v>16.8300974239806</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.17605757459907</v>
+        <v>15.18950387715881</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.0800181317346</v>
+        <v>13.09357095862762</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.972002204424129</v>
+        <v>9.961572568725607</v>
       </c>
     </row>
     <row r="9">
@@ -731,98 +731,98 @@
         <v>216</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.63431794814425</v>
+        <v>-6.621858708739872</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.781319792271773</v>
+        <v>-7.768470711402792</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.792230600574428</v>
+        <v>-6.779278896007469</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.50980153400107</v>
+        <v>-2.496869091338638</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.894827845702274</v>
+        <v>-4.881761186991184</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.52334334041926</v>
+        <v>-5.510339922797101</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.072042314224134</v>
+        <v>-6.059010726737725</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.229918455477474</v>
+        <v>-4.216766156517068</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.518280063611613</v>
+        <v>-1.505104095031676</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5183400811284784</v>
+        <v>-0.5049529392925507</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.573134731803322</v>
+        <v>-2.559691481355522</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.539198120241252</v>
+        <v>-2.525755241611648</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.034149413243469</v>
+        <v>-2.020598113622512</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.636774639646823</v>
+        <v>-3.647204275344976</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1408</t>
+          <t>X ≈ -0.1407</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>271</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6425763524973931</v>
+        <v>0.6550341869380958</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2278608414451426</v>
+        <v>-0.2150132903916244</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.356547175742314</v>
+        <v>-1.343599089866601</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6111352974755633</v>
+        <v>0.6240632731603952</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.661436725830221</v>
+        <v>-0.6483736937162874</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.3650462370441403</v>
+        <v>-0.35204539450352</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.659389290738389</v>
+        <v>-2.646361261479399</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.654221239313813</v>
+        <v>-1.641072161728907</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.084304562321826</v>
+        <v>-2.071132509586008</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.934304402348687</v>
+        <v>-2.92092104379109</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.033570797035104</v>
+        <v>-2.020129648499562</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.580901557609508</v>
+        <v>-4.56746062208525</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.264462741008494</v>
+        <v>-4.250912435932221</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.016028432184747</v>
+        <v>-4.026458067882899</v>
       </c>
     </row>
     <row r="11">
@@ -835,306 +835,306 @@
         <v>205</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.237289256278842</v>
+        <v>-2.224846259272681</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.75800821249377</v>
+        <v>-6.745180119335764</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.096894881232984</v>
+        <v>-9.083966766539497</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.485666961047215</v>
+        <v>-8.472757940704348</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.024988066982907</v>
+        <v>-9.011941817411468</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.272223107672936</v>
+        <v>-7.259235713637914</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-10.27931065074146</v>
+        <v>-10.2662954723216</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.72393626275208</v>
+        <v>-11.710799641648</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-14.22395723389253</v>
+        <v>-14.21079681525867</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-17.02664166850008</v>
+        <v>-17.01326864428508</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-20.16067960046536</v>
+        <v>-20.14724755328692</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-20.13275843002385</v>
+        <v>-20.11932315198299</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-19.09671088611865</v>
+        <v>-19.08316333587015</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-17.39016217352216</v>
+        <v>-17.40059180922032</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06128</t>
+          <t>X ≈ -0.06125</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>187</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.450298065817087</v>
+        <v>3.180629511676656</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.355815083793566</v>
+        <v>7.077462450375684</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.816575813135557</v>
+        <v>8.534315828625672</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9.274296678435796</v>
+        <v>8.995424399072618</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.60410350194365</v>
+        <v>10.3217456962641</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.544245765328895</v>
+        <v>8.263279761896094</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>7.145087043914792</v>
+        <v>6.862085889693674</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.90802543024153</v>
+        <v>5.624840735675342</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>6.144672820891252</v>
+        <v>5.861208173208539</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>6.116588182838136</v>
+        <v>5.829312501625026</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>5.141618838004568</v>
+        <v>4.851745427285437</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.410024045682768</v>
+        <v>4.117494211893124</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.762685276541653</v>
+        <v>3.466430540160545</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.013255069206409</v>
+        <v>4.002825433508256</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.02153</t>
+          <t>X ≈ -0.0215</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.015855559526692</v>
+        <v>-0.9957675156828643</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.344281190649376</v>
+        <v>1.353442430857271</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.94078990778457</v>
+        <v>1.948770056003212</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.0842759958493815</v>
+        <v>0.09879717978949287</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.030134263130847</v>
+        <v>2.035755151446374</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.324060057224436</v>
+        <v>3.323228190982341</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.227552365251</v>
+        <v>5.218715851518155</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.76516171825304</v>
+        <v>3.761548197830535</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.196516772909021</v>
+        <v>5.185714556159134</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>8.820356076289713</v>
+        <v>8.791241304383959</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.623182156999846</v>
+        <v>6.606342126321785</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>11.13280641091517</v>
+        <v>11.09616582323168</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>13.69416134754027</v>
+        <v>13.64631199962113</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>11.7446515626749</v>
+        <v>11.89184963004556</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.01822</t>
+          <t>X ≈ 0.01825</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>181</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.874653789823107</v>
+        <v>-3.862131500147484</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.696172154168707</v>
+        <v>-7.683262344592656</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.776123733693474</v>
+        <v>-4.763116602275872</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.093384413240543</v>
+        <v>-4.080405270842078</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.974347064776929</v>
+        <v>-2.961236260401989</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.229391314906692</v>
+        <v>-3.216348418612327</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.104180280797635</v>
+        <v>-1.091114026497159</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.571363679579136</v>
+        <v>-1.558182670283898</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5775811856199056</v>
+        <v>0.5907799245746688</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.8250301872535815</v>
+        <v>-0.8116250596007504</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.285133615500783</v>
+        <v>2.298590909211001</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.976975336382012</v>
+        <v>3.990427625102122</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.661693101127838</v>
+        <v>4.675249147479441</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.673845372630652</v>
+        <v>7.6634157369325</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.05798</t>
+          <t>X ≈ 0.05801</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>241</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.033532634146781</v>
+        <v>1.046054923822403</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2518345398548121</v>
+        <v>0.2647443494308632</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.101779111266524</v>
+        <v>1.114786242684126</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.061907762546134</v>
+        <v>2.074886904944599</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.523486547473965</v>
+        <v>1.536597351848904</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2537603114907867</v>
+        <v>-0.2407174151964213</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.753431788099256</v>
+        <v>-0.74036553379878</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.295303983561155</v>
+        <v>-3.282122974265917</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.186179388415759</v>
+        <v>-4.172980649460996</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.376553536099188</v>
+        <v>-3.363148408446357</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.411182379088963</v>
+        <v>-4.397725085378745</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.206674740415743</v>
+        <v>-5.193222451695632</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.211991592024447</v>
+        <v>-5.198435545672844</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.622021297092559</v>
+        <v>-6.632450932790711</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.09773</t>
+          <t>X ≈ 0.09774</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>350</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.792275965504309</v>
+        <v>1.804798255179932</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.819297647459919</v>
+        <v>-1.806387837883868</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9286907888006084</v>
+        <v>0.9416979202182105</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.226770364306176</v>
+        <v>-1.213791221907712</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6223344365211432</v>
+        <v>-0.6092236321462039</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.3248924988054824</v>
+        <v>-0.311849602511117</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7332309267794201</v>
+        <v>0.7462971810798962</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.3053810434307209</v>
+        <v>-0.2922000341354831</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.347904784672693</v>
+        <v>1.361103523627456</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.069208171073399</v>
+        <v>1.08261329872623</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2930262753271222</v>
+        <v>0.30648356903734</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.041695146958297</v>
+        <v>2.055147435678407</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.335726250299039</v>
+        <v>3.349282296650642</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.442590439718217</v>
+        <v>4.432160804020064</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>262</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1783174049808665</v>
+        <v>0.1908396946564892</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.910255242398236</v>
+        <v>3.923165051974287</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.568821650305473</v>
+        <v>6.581828781723075</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.172357225661102</v>
+        <v>5.185336368059566</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.778974178527818</v>
+        <v>5.792084982902757</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.931377948304593</v>
+        <v>4.944420844598959</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.663438124162049</v>
+        <v>8.676504378462525</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.051216557441613</v>
+        <v>7.064397566736851</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.608537281946333</v>
+        <v>6.621736020901096</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>8.048488432796262</v>
+        <v>8.061893560449093</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.698696940539847</v>
+        <v>6.712154234250065</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.588041929946307</v>
+        <v>5.601494218666417</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.457863654879212</v>
+        <v>7.471419701230815</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.562546819216571</v>
+        <v>6.552117183518419</v>
       </c>
     </row>
     <row r="18">
@@ -1196,49 +1196,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.194587745497337</v>
+        <v>-0.4809160305343525</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6567360711052714</v>
+        <v>-0.9492449807410352</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-3.925167996092604</v>
+        <v>-4.201159222638864</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.093765438197806</v>
+        <v>-6.356648364764858</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.632186653269912</v>
+        <v>-6.894937917860425</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-4.88327817393975</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.120627858113941</v>
+        <v>-4.396559961777413</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.139535394826552</v>
+        <v>-1.435057176992657</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.499385855721428</v>
+        <v>-3.210325047801078</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.625373109714879</v>
+        <v>-2.345958129845293</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.404839077710612</v>
+        <v>-3.122087859534055</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.071605345652543</v>
+        <v>-1.373423992893017</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-3.215997887631865</v>
+        <v>-2.936431989063507</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.690414486390182</v>
+        <v>-4.424982053122754</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.397866027616047</v>
+        <v>2.710340800066682</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.503683718999682</v>
+        <v>3.831395144161377</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>4.73924979501178</v>
+        <v>5.075968021701421</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>3.782546405880161</v>
+        <v>4.113296990426399</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.787603451677555</v>
+        <v>4.121455524762339</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8241758241758248</v>
+        <v>1.140141029807317</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.977949197444353</v>
+        <v>-1.676809766617311</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.988610857095352</v>
+        <v>-2.690326497835812</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.506132482408084</v>
+        <v>-2.751308654358589</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-2.812779406566442</v>
+        <v>-3.054779363256685</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.873771616941994</v>
+        <v>1.658552265368307</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>0.6000342428602963</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4009436416034546</v>
+        <v>0.1798833895468874</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.824578017358071</v>
+        <v>2.591411389500195</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>211</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4.852533243771127</v>
+        <v>4.86505553344675</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6.558495175830508</v>
+        <v>6.571404985406559</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9.007228364968491</v>
+        <v>9.020235496386093</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.137481497576012</v>
+        <v>9.150460639974476</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9.546927581082045</v>
+        <v>9.560038385456984</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11.26617046666497</v>
+        <v>11.27921336295934</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.65537039868187</v>
+        <v>11.66843665298235</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>13.55785524634587</v>
+        <v>13.57103625564111</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12.54898806158533</v>
+        <v>12.56218680054009</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>10.27706192869013</v>
+        <v>10.29046705634296</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.07230860437255</v>
+        <v>10.08576589808277</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.58062541100705</v>
+        <v>10.59407769972716</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11.10823809864035</v>
+        <v>11.12179414499195</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14.20156132665123</v>
+        <v>14.19113169095308</v>
       </c>
     </row>
     <row r="21">
@@ -1355,46 +1355,46 @@
         <v>183</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.591798975947682</v>
+        <v>-6.57927668627206</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.924684064321774</v>
+        <v>-4.911774254745723</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.412448945781719</v>
+        <v>-6.399441814364117</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.37509198803761</v>
+        <v>-7.362112845639146</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.552857465404927</v>
+        <v>-9.539746661029987</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.616071265394119</v>
+        <v>-7.603028369099754</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.793701157529817</v>
+        <v>-8.780634903229341</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-10.3537807311747</v>
+        <v>-10.34059972187946</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-9.321884442493619</v>
+        <v>-9.308685703538856</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-10.17200962752158</v>
+        <v>-10.15860449986874</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.190970602112316</v>
+        <v>-8.177513308402098</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-10.3423797944937</v>
+        <v>-10.32892750577358</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-10.2161863180069</v>
+        <v>-10.20263027165529</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-12.69870542288908</v>
+        <v>-12.70913505858724</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>135</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.580635753864101</v>
+        <v>1.593158043539724</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.475382303544642</v>
+        <v>-4.46247249396859</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-9.314695454585639</v>
+        <v>-9.301688323168037</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-6.221479359015177</v>
+        <v>-6.208500216616713</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.500641314828044</v>
+        <v>-7.487530510453105</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.90690308081613</v>
+        <v>-10.89386018452176</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-13.95459976105137</v>
+        <v>-13.94153350675089</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-12.19956093761065</v>
+        <v>-12.18637992831541</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-16.70500526823739</v>
+        <v>-16.69180652928263</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-16.07364897178384</v>
+        <v>-16.06024384413101</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-16.27840229610142</v>
+        <v>-16.2649450023912</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-14.02179691653381</v>
+        <v>-14.0083446278137</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-14.44205152747867</v>
+        <v>-14.42849548112707</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-14.93307093594312</v>
+        <v>-14.94350057164127</v>
       </c>
     </row>
     <row r="23">
@@ -1459,150 +1459,150 @@
         <v>56</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-6.064866891638445</v>
+        <v>-6.052344601962822</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.462154790316987</v>
+        <v>-9.449244980740936</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.071309211199392</v>
+        <v>-8.058302079781789</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.726770364306283</v>
+        <v>-9.713791221907819</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.693763007949777</v>
+        <v>-6.680652203574837</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-11.75346392737708</v>
+        <v>-11.74042103108271</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-8.266769073220679</v>
+        <v>-8.253702818920203</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.376809614859319</v>
+        <v>-3.363628605564081</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.43780950104162</v>
+        <v>-3.424610762086857</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.287934686069548</v>
+        <v>-4.274529558416717</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-4.492688010387027</v>
+        <v>-4.47923071667681</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.672590567327319</v>
+        <v>-2.659138278607209</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.878559463986598</v>
+        <v>-4.865003417634995</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-8.200266703138787</v>
+        <v>-8.210696338836939</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.4157</t>
+          <t>X ≈ 0.4158</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>40</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.493438320210117</v>
+        <v>-2.480916030534495</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.39498806682591</v>
+        <v>3.407897876401961</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.499880639770964</v>
+        <v>-4.486873508353362</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-16.86962750716332</v>
+        <v>-16.85664836476486</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-9.90804872223535</v>
+        <v>-9.89493791786041</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-9.610606784519547</v>
+        <v>-9.597563888225181</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-9.695340501791968</v>
+        <v>-9.682274247491492</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-10.16252390057361</v>
+        <v>-10.14934289127837</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15.22352378675591</v>
+        <v>-15.21032504780115</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-13.57364897178384</v>
+        <v>-13.56024384413101</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-8.778402296101561</v>
+        <v>-8.764945002391343</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-9.164273749700889</v>
+        <v>-9.150717703349287</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.414552417424886</v>
+        <v>-6.424982053123038</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.4555</t>
+          <t>X ≈ 0.4556</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>40</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.006561679790018</v>
+        <v>5.01908396946564</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.394988066825633</v>
+        <v>3.407897876401684</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5001193602293128</v>
+        <v>0.5131264916469149</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6303724928366847</v>
+        <v>0.6433516352351489</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.408048722235634</v>
+        <v>-2.394937917860695</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.389393215480176</v>
+        <v>0.4024361117745414</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.195340501792252</v>
+        <v>-2.182274247491776</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.337476099426532</v>
+        <v>2.350657108721769</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.776476213244088</v>
+        <v>4.789674952198851</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.073648971783832</v>
+        <v>-1.060243844131001</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.278402296101412</v>
+        <v>-1.264945002391194</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.244019138755853</v>
+        <v>-1.230566850035743</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.16427374970074</v>
+        <v>-4.150717703349137</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.41455241742446</v>
+        <v>-6.424982053122612</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>61</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.801643647003139</v>
+        <v>9.814165936678762</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>18.02613560780937</v>
+        <v>18.03904541738542</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>15.9919226389177</v>
+        <v>16.0049297703353</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>16.1221757715252</v>
+        <v>16.13515491392366</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>17.22309881874816</v>
+        <v>17.2362096231231</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>17.52054075646363</v>
+        <v>17.533583652758</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19.07515130148658</v>
+        <v>19.08821755578705</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>18.60796790270498</v>
+        <v>18.62114891200022</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>20.18631227881786</v>
+        <v>20.19951101777262</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>19.33618709378993</v>
+        <v>19.34959222144276</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>19.13143376947235</v>
+        <v>19.14489106318257</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>24.08384971370295</v>
+        <v>24.09730200242306</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>26.94228362734824</v>
+        <v>26.95583967369984</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>28.83134922191965</v>
+        <v>28.8209195862215</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>51</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.290875405280218</v>
+        <v>8.303397694955841</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.640086106041451</v>
+        <v>8.652995915617502</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>14.12757034062133</v>
+        <v>14.14057747203893</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>18.17939210067981</v>
+        <v>18.19237124307828</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>19.60175519933308</v>
+        <v>19.61486600370802</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>19.89919713704886</v>
+        <v>19.91224003334322</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.89289479232554</v>
+        <v>15.90596104662602</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>19.34728002099502</v>
+        <v>19.36046103029026</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>17.32549582108722</v>
+        <v>17.33869456004199</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>14.51458632233381</v>
+        <v>14.52799144998664</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>16.27061731174172</v>
+        <v>16.28407460545193</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>22.18735341026357</v>
+        <v>22.20080569898368</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>17.84553017186763</v>
+        <v>17.85908621821923</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>16.13446719041853</v>
+        <v>16.12403755472038</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>40</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>20.00656167979002</v>
+        <v>20.01908396946565</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>18.39498806682577</v>
+        <v>18.40789787640182</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20.50011936022918</v>
+        <v>20.51312649164678</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>15.63037249283668</v>
+        <v>15.64335163523514</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.59195127776451</v>
+        <v>12.60506208213945</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.38939321548017</v>
+        <v>15.40243611177453</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>15.30465949820789</v>
+        <v>15.31772575250837</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>17.33747609942639</v>
+        <v>17.35065710872163</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.77647621324409</v>
+        <v>14.78967495219885</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11.42635102821616</v>
+        <v>11.43975615586899</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.721597703898581</v>
+        <v>8.735054997608799</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.255980861244076</v>
+        <v>6.269433149964186</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.335726250299253</v>
+        <v>3.349282296650856</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.085447582575469</v>
+        <v>1.075017946877317</v>
       </c>
     </row>
     <row r="29">
@@ -1771,46 +1771,46 @@
         <v>60</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.506561679790025</v>
+        <v>7.519083969465647</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.89498806682577</v>
+        <v>10.90789787640182</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.166786026895849</v>
+        <v>7.179793158313451</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.963705826170006</v>
+        <v>8.97668496856847</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.75861794443118</v>
+        <v>6.771728748806119</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.056059882146783</v>
+        <v>7.069102778441149</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.30465949820789</v>
+        <v>10.31772575250837</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.170809432759718</v>
+        <v>8.183990442054956</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.776476213244088</v>
+        <v>9.789674952198851</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.92635102821616</v>
+        <v>8.939756155868992</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.721597703898581</v>
+        <v>8.735054997608799</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.755980861244012</v>
+        <v>3.769433149964122</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.669059583632396</v>
+        <v>6.682615629983999</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.918780915908677</v>
+        <v>1.908351280210525</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>75</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-13.82677165354333</v>
+        <v>-13.8142493638677</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.438345266507568</v>
+        <v>-7.425435456931517</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-9.166547306437494</v>
+        <v>-9.153540175019891</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.036294173830008</v>
+        <v>-5.023315031431544</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2413820555688275</v>
+        <v>-0.2282712511938882</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.61060678451981</v>
+        <v>-2.597563888225444</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.362007168458774</v>
+        <v>-1.348940914158298</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.162523900573611</v>
+        <v>-3.149342891278373</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.223523786755912</v>
+        <v>-3.210325047801149</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.07364897178384</v>
+        <v>-4.060243844131008</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.278402296101419</v>
+        <v>-4.264945002391201</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.910685805422652</v>
+        <v>-6.897233516702542</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.330940416367554</v>
+        <v>-7.317384370015951</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.747885750757931</v>
+        <v>-5.758315386456083</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>37</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.844789671561252</v>
+        <v>-3.832267381885629</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-10.86176868993095</v>
+        <v>-10.8488588803549</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-27.47285361274379</v>
+        <v>-27.45984648132619</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-27.34260048013626</v>
+        <v>-27.32962133773779</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-25.17831899250572</v>
+        <v>-25.16520818813078</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-19.47547164938466</v>
+        <v>-19.46242875309029</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-22.26290806935964</v>
+        <v>-22.24984181505916</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-25.43279417084388</v>
+        <v>-25.41961316154864</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-22.79109135432348</v>
+        <v>-22.77789261536871</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-29.04662194475681</v>
+        <v>-29.03321681710398</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-21.14326716096625</v>
+        <v>-21.12980986725603</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-21.10888400362085</v>
+        <v>-21.09543171490074</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-18.82643591186305</v>
+        <v>-18.81287986551145</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-18.57671457958676</v>
+        <v>-18.58714421528492</v>
       </c>
     </row>
     <row r="32">
@@ -1927,46 +1927,46 @@
         <v>17</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>12.21244403273111</v>
+        <v>12.22496632240674</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>16.48322336094333</v>
+        <v>16.49613317051939</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.20600171317035</v>
+        <v>10.21900884458795</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>16.21860778695433</v>
+        <v>16.23158692935279</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>21.56253951305854</v>
+        <v>21.57565031743348</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>15.97762850959782</v>
+        <v>15.99067140589219</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>15.89289479232546</v>
+        <v>15.90596104662593</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.543358452367563</v>
+        <v>9.556539461662801</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.600005625008798</v>
+        <v>3.613204363963561</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.749880439980871</v>
+        <v>2.763285567633702</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.42748005683967</v>
+        <v>8.440937350549888</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.461863214185186</v>
+        <v>8.475315502905296</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.041608603240284</v>
+        <v>8.055164649591887</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>14.17368287669305</v>
+        <v>14.1632532409949</v>
       </c>
     </row>
     <row r="33">
@@ -1979,46 +1979,46 @@
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.434614790798165</v>
+        <v>-5.422092501122542</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.60087041976694</v>
+        <v>10.61378022934299</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.08835465434683</v>
+        <v>16.10136178576443</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>22.10096072813079</v>
+        <v>22.11393987052926</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>21.56253951305858</v>
+        <v>21.57565031743352</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>21.85998145077428</v>
+        <v>21.87302434706865</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>27.65760067467844</v>
+        <v>27.67066692897892</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>27.19041727589697</v>
+        <v>27.20359828519221</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>33.01177033089115</v>
+        <v>33.02496906984591</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>32.16164514586318</v>
+        <v>32.17505027351601</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>26.07453888036916</v>
+        <v>26.08799617407938</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.34421615536162</v>
+        <v>14.35766844408173</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.041608603240284</v>
+        <v>8.055164649591887</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.408976994340108</v>
+        <v>2.398547358641956</v>
       </c>
     </row>
     <row r="34">
@@ -2031,46 +2031,46 @@
         <v>31</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>12.02269071204806</v>
+        <v>12.03521300172368</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>13.63692355069673</v>
+        <v>13.64983336027278</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.24205484410014</v>
+        <v>13.25506197551774</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.14650152509474</v>
+        <v>10.15948066749321</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16.05969321324841</v>
+        <v>16.07280401762335</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.80874805418985</v>
+        <v>22.82179095048421</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.27240143369179</v>
+        <v>16.28546768799227</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>19.03102448652316</v>
+        <v>19.0442054958184</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>18.97002460034086</v>
+        <v>18.98322333929562</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.89409296370006</v>
+        <v>14.90749809135289</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.91514609099535</v>
+        <v>17.92860338470557</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.72372279672791</v>
+        <v>14.73717508544802</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.07766173417007</v>
+        <v>11.09121778052167</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.875770163220558</v>
+        <v>4.865340527522406</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-50-200 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-50-200 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2214,49 +2214,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2928602482971883</v>
+        <v>0.2918925562277224</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2033490998096568</v>
+        <v>0.2023764040091791</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2827280558813499</v>
+        <v>0.2817278723678172</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.4269956701198652</v>
+        <v>0.4259603308873139</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2608356175802697</v>
+        <v>0.2598331233264517</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2908521353675511</v>
+        <v>0.2898465518973623</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1945724526369759</v>
+        <v>0.1935895866522088</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.00247268418436164</v>
+        <v>-0.003413551800640846</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.001886049309661075</v>
+        <v>0.0009425578326585082</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.03982883342873578</v>
+        <v>-0.04077663101625717</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.05082669384616878</v>
+        <v>-0.05177564548625213</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.07487345288717506</v>
+        <v>0.07389240162994071</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2331621477350083</v>
+        <v>0.2321328477914406</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1384098806005341</v>
+        <v>0.139120510979815</v>
       </c>
     </row>
     <row r="7">
@@ -2266,101 +2266,101 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3844</v>
+        <v>3845</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3196288304252306</v>
+        <v>0.3184618854843109</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2518345398548121</v>
+        <v>0.2506513117142362</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3898729270255501</v>
+        <v>0.3886451638459576</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.5343683413058002</v>
+        <v>0.5331052020315141</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3995038342140305</v>
+        <v>0.3982639503283352</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.5036195913887838</v>
+        <v>0.5023582503678412</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3812629778235745</v>
+        <v>0.3800310484585196</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05825532020561752</v>
+        <v>0.05709699446558858</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.01437855422798151</v>
+        <v>-0.0155198529959506</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.07053046866533919</v>
+        <v>-0.07167538479091462</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1567490598134</v>
+        <v>-0.1578763953225888</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.003769528771591979</v>
+        <v>-0.004936488715365783</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1887821670741445</v>
+        <v>0.1875558275919573</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1151041902757015</v>
+        <v>0.1159802355638462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.2402</t>
+          <t>X &gt; -0.2401</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3725</v>
+        <v>3726</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3155504438349652</v>
+        <v>0.3139489066146126</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2969147459801675</v>
+        <v>0.2952708031005926</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.451939488708831</v>
+        <v>0.4502418248017221</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5433577672677359</v>
+        <v>0.5416385731366375</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3410139451453276</v>
+        <v>0.3393324971327516</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3585868934871357</v>
+        <v>0.3569085274146033</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1814011916698419</v>
+        <v>0.1797670061917387</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.02985169473067373</v>
+        <v>-0.03144364154632484</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.07607070364598911</v>
+        <v>-0.07765284195821209</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2141692184987676</v>
+        <v>-0.2157398226832896</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2429945707795369</v>
+        <v>-0.2445642032493467</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1399139603283004</v>
+        <v>-0.1415110560444646</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.07217284181816552</v>
+        <v>0.07050580080955626</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1460960415856789</v>
+        <v>-0.1447888164077824</v>
       </c>
     </row>
     <row r="9">
@@ -2370,101 +2370,101 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3606</v>
+        <v>3607</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.09014830592984424</v>
+        <v>0.08814474294630514</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.04199369105151618</v>
+        <v>-0.0440225436037025</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1310289538150187</v>
+        <v>0.1289363313372149</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1934255901818176</v>
+        <v>0.1913195644582615</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.08503564844224343</v>
+        <v>0.0829381883341398</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06565220828592544</v>
+        <v>0.06357027498338397</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.1700152872889262</v>
+        <v>-0.172036284016265</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4559901242723967</v>
+        <v>-0.4579506964264439</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4741468828511799</v>
+        <v>-0.4761057786981553</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.727388583972207</v>
+        <v>-0.7293105846461003</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.8059722600803596</v>
+        <v>-0.8078812904798411</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.6453495156961182</v>
+        <v>-0.647302787968826</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3570932673055438</v>
+        <v>-0.3591434239701314</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4799988955166725</v>
+        <v>-0.4782118840071448</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1607</t>
+          <t>X &gt; -0.1606</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3390</v>
+        <v>3391</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5186098725611146</v>
+        <v>0.5155587050708164</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.451131511858101</v>
+        <v>0.4480095425787241</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.5721569962185882</v>
+        <v>0.568975991940718</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3656666104837356</v>
+        <v>0.3625518704600736</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.4023366852372945</v>
+        <v>0.3991797291982735</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.4217651989998785</v>
+        <v>0.4186173415479999</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2060430719494235</v>
+        <v>0.2029523563930056</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.2155274341425155</v>
+        <v>-0.218521578355201</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.4076180430151126</v>
+        <v>-0.4105606190614566</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7407084885781785</v>
+        <v>-0.7436017233651739</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.6933742972803145</v>
+        <v>-0.6962944425797701</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.5246795161144817</v>
+        <v>-0.5276490781525922</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2502365925201175</v>
+        <v>-0.2533120429719347</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2788592020853713</v>
+        <v>-0.2763533300322223</v>
       </c>
     </row>
     <row r="11">
@@ -2474,309 +2474,309 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3119</v>
+        <v>3120</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.5078388189981951</v>
+        <v>0.5034440077675981</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5101270000739291</v>
+        <v>0.5055990258271095</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.7397359736477043</v>
+        <v>0.735100301931034</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.344338616198776</v>
+        <v>0.3398372582383402</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4947645769972411</v>
+        <v>0.4901691450988608</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4901287447414404</v>
+        <v>0.4855563163781085</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.4550113856039246</v>
+        <v>0.4504408148684576</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.09052390057361492</v>
+        <v>-0.09496029370959747</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.261936078689331</v>
+        <v>-0.2663250478011463</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5501139093438709</v>
+        <v>-0.5544820003409967</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5769288816235232</v>
+        <v>-0.5813074743732756</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1722472707649629</v>
+        <v>-0.1767551908430605</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.09854676311962152</v>
+        <v>0.09391542705763101</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.04585155820861075</v>
+        <v>0.04937692123621673</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.08116</t>
+          <t>X &gt; -0.08113</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2914</v>
+        <v>2915</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.7009586732987358</v>
+        <v>0.6953134776623742</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.021440561699315</v>
+        <v>1.015516598643025</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.43174329185311</v>
+        <v>1.425635035734274</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9655298115781221</v>
+        <v>0.9595909514744534</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.164479502191462</v>
+        <v>1.158413655326861</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.036210463940122</v>
+        <v>1.030215790187128</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.210171309231512</v>
+        <v>1.204104944842378</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.7278870583305022</v>
+        <v>0.7219340686668545</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7202925887151466</v>
+        <v>0.7143324864454286</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6090103839392569</v>
+        <v>0.6029969917716969</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.8007886535043411</v>
+        <v>0.7946848810906317</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.231975374275557</v>
+        <v>1.225723859597309</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.448933797468918</v>
+        <v>1.44256076029955</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.272475722589128</v>
+        <v>1.276561686156839</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.04141</t>
+          <t>X &gt; -0.04138</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5124267824293156</v>
+        <v>0.5249490721049384</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5870701782627137</v>
+        <v>0.5999799878387648</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9253393015781484</v>
+        <v>0.9383464329957505</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3957683872648232</v>
+        <v>0.4087475296632874</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.5171712191134787</v>
+        <v>0.530282023488418</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5213580248643268</v>
+        <v>0.5344009211586922</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.8031932225480602</v>
+        <v>0.8162594768485363</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.372666715262163</v>
+        <v>0.3858477245574008</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3483237205754577</v>
+        <v>0.3615224595302209</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.231336365459569</v>
+        <v>0.2447414931124001</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5031226305848051</v>
+        <v>0.5165799242950229</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.014045377373051</v>
+        <v>1.027497666093161</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.290271704844571</v>
+        <v>1.303827751196174</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.0845308242329</v>
+        <v>1.089680703475487</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.001654</t>
+          <t>X &gt; -0.001627</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>2526</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.634035947406808</v>
+        <v>0.6465582370824308</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.526817045448098</v>
+        <v>0.5397268550241492</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8445374124857068</v>
+        <v>0.8575445439033089</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.420554598933272</v>
+        <v>0.4335337413317362</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.3967810481524694</v>
+        <v>0.4098918525274087</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.2983401671824666</v>
+        <v>0.311383063476832</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4511361411215873</v>
+        <v>0.4642023954220633</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.10271758794579</v>
+        <v>0.1158985972410278</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.03745886197364712</v>
+        <v>-0.02426012301888392</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.4521129464473361</v>
+        <v>-0.438707818794505</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.01613452100071555</v>
+        <v>0.02959181471093331</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2088708058204105</v>
+        <v>0.2223230945405206</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3032638591668899</v>
+        <v>0.3168199055184928</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.2362789364946352</v>
+        <v>0.225849300796483</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.0381</t>
+          <t>X &gt; 0.03813</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2345</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9820414239264821</v>
+        <v>0.9945637136021048</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.161512587081631</v>
+        <v>1.174422396657683</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.278370959376296</v>
+        <v>1.291378090793899</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7689652433697205</v>
+        <v>0.7819443857681847</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6569832607069372</v>
+        <v>0.6700940650818765</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5706298892541639</v>
+        <v>0.5836727855485293</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5711840184637538</v>
+        <v>0.5842502727642298</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2319323894050669</v>
+        <v>0.2451133987003047</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.08493103622286924</v>
+        <v>-0.07173229726810604</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4233291423595276</v>
+        <v>-0.4099240147066965</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.1589993110267898</v>
+        <v>-0.145542017316572</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.0819722304404209</v>
+        <v>-0.06851994172031084</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.03314368573500559</v>
+        <v>-0.01958763938340269</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3377933555909109</v>
+        <v>-0.3482229912890631</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.07786</t>
+          <t>X &gt; 0.07788</t>
         </is>
       </c>
       <c r="B16" t="n">
         <v>2104</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9761434288394568</v>
+        <v>0.9886657185150796</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.265710500285842</v>
+        <v>1.278620309861893</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.298598447681648</v>
+        <v>1.31160557909925</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6208667894146274</v>
+        <v>0.6338459318130916</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5577307454451201</v>
+        <v>0.5708415498200594</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.6650586147197188</v>
+        <v>0.6781015110140842</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7229104487782365</v>
+        <v>0.7359767030787125</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.63595518687886</v>
+        <v>0.6491361961740978</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3848412322554964</v>
+        <v>0.3980399712102596</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.08505581589029987</v>
+        <v>-0.07165068823746878</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3280615822255797</v>
+        <v>0.3415188759357974</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5050302909018072</v>
+        <v>0.5184825796219172</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5600608510595606</v>
+        <v>0.5736168974111635</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3820255293434514</v>
+        <v>0.3715958936452992</v>
       </c>
     </row>
     <row r="17">
@@ -2789,46 +2789,46 @@
         <v>1754</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8132891598356338</v>
+        <v>0.8258114495112565</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.881305056563505</v>
+        <v>1.894214866139556</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.372411264448104</v>
+        <v>1.385418395865706</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.9895515122209417</v>
+        <v>1.002530654619406</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.7932055537052136</v>
+        <v>0.8063163580801529</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.8625973203832444</v>
+        <v>0.8756402166776098</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7208510603515563</v>
+        <v>0.7339173146520324</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.823793089164127</v>
+        <v>0.8369740984593648</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.1926677753877541</v>
+        <v>0.2058665143425173</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.315382153083732</v>
+        <v>-0.3019770254309009</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3350526639898064</v>
+        <v>0.3485099577000241</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.1983981930570096</v>
+        <v>0.2118504817771196</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.006193753149737802</v>
+        <v>0.0197497995013407</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4282354276868645</v>
+        <v>-0.4386650633850167</v>
       </c>
     </row>
     <row r="18">
@@ -2841,46 +2841,46 @@
         <v>1492</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9247922427927051</v>
+        <v>0.9373145324683279</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.525014876477243</v>
+        <v>1.537924686053294</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4599048830173871</v>
+        <v>0.4729120144349892</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2550373721932431</v>
+        <v>0.2680165145917073</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.08231145681993723</v>
+        <v>-0.06920065244499796</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1481063522093891</v>
+        <v>0.1611492485037544</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6738927806124835</v>
+        <v>-0.6608265263120074</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2697625064717357</v>
+        <v>-0.2565814971764979</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9339795508309763</v>
+        <v>-0.9207808118762131</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.784104735858904</v>
+        <v>-1.770699608206073</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7824237438225978</v>
+        <v>-0.7689664501123801</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.7480405864771669</v>
+        <v>-0.7345882977570568</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.302343454794716</v>
+        <v>-1.288787408443113</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.655839280695382</v>
+        <v>-1.666268916393534</v>
       </c>
     </row>
     <row r="19">
@@ -2890,49 +2890,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.072570784494118</v>
+        <v>1.125765822161163</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.813045729951718</v>
+        <v>1.868414201382834</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.038814352641928</v>
+        <v>1.093992095291426</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.093194951106788</v>
+        <v>1.148287094612513</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.7823913384625385</v>
+        <v>0.8377879743186369</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.7763431396076399</v>
+        <v>0.8314414268846377</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2188609873763312</v>
+        <v>-0.1644306635888171</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1549366471593387</v>
+        <v>-0.09998829750464466</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.5952992040548537</v>
+        <v>-0.6165513196310712</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.673041991510701</v>
+        <v>-1.694260548762749</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4362171671181088</v>
+        <v>-0.4562889659447293</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.7053241463432371</v>
+        <v>-0.6497012463912313</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.049706223145499</v>
+        <v>-1.06985209970464</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.255220095725051</v>
+        <v>-1.299697315081751</v>
       </c>
     </row>
     <row r="20">
@@ -2945,46 +2945,46 @@
         <v>1134</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8575316974267153</v>
+        <v>0.8700539871023381</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.538727043898078</v>
+        <v>1.551636853474129</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.43839096516745</v>
+        <v>0.4513980965850521</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.6568275192917028</v>
+        <v>0.669806661690167</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.2947731472530464</v>
+        <v>0.3078839516279857</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.768581928002213</v>
+        <v>0.7816248242965784</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.06656426011265637</v>
+        <v>0.0796305144131324</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3048482334651936</v>
+        <v>0.3180292427604314</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2852521818176399</v>
+        <v>-0.2720534428628767</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.488111052912586</v>
+        <v>-1.474705925259755</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.8110301620626146</v>
+        <v>-0.7975728683523968</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8648304262339437</v>
+        <v>-0.8513781375138336</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.285085037178845</v>
+        <v>-1.271528990827242</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.917197920070102</v>
+        <v>-1.927627555768254</v>
       </c>
     </row>
     <row r="21">
@@ -2997,46 +2997,46 @@
         <v>923</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.05573517828148056</v>
+        <v>-0.04321288860585781</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.3911960841605477</v>
+        <v>0.4041058937365989</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.52046568852488</v>
+        <v>-1.507458557107277</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.281870194053894</v>
+        <v>-1.26889105165543</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.820291409126064</v>
+        <v>-1.807180604751125</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.631191833273888</v>
+        <v>-1.618148936979523</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.582664445454085</v>
+        <v>-2.569598191153609</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.724820758645116</v>
+        <v>-2.711639749349878</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.219190092281373</v>
+        <v>-3.20599135332661</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.177657639172793</v>
+        <v>-4.164252511519962</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.298987344855476</v>
+        <v>-3.285530051145258</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.48128891123703</v>
+        <v>-3.46783662251692</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.118228245908909</v>
+        <v>-4.104672199557307</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.601984703448437</v>
+        <v>-5.612414339146589</v>
       </c>
     </row>
     <row r="22">
@@ -3049,98 +3049,98 @@
         <v>740</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.560615733844081</v>
+        <v>1.573138023519704</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.705798877636575</v>
+        <v>1.718708687212626</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3106914505816292</v>
+        <v>-0.297684319164027</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.224967087431267</v>
+        <v>0.2379462298297312</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.09195127776451528</v>
+        <v>0.1050620821394546</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.1511473250603714</v>
+        <v>-0.138104428766006</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.046691853143464</v>
+        <v>-1.033625598842988</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.8381995762492878</v>
+        <v>-0.82501856695405</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.710010273242403</v>
+        <v>-1.69681153428764</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.695270593405461</v>
+        <v>-2.68186546575263</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.089213106912226</v>
+        <v>-2.075755813202008</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.784559679296528</v>
+        <v>-1.771107390576418</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.610219695646833</v>
+        <v>-2.59666364929523</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.846984849857037</v>
+        <v>-3.857414485555189</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.3561</t>
+          <t>X &gt; 0.3562</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>605</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.556148456649531</v>
+        <v>1.568670746325154</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.085070711453874</v>
+        <v>3.097980521029925</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.698466467667195</v>
+        <v>1.711473599084798</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.663430344076339</v>
+        <v>1.676409486474803</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.786166153797566</v>
+        <v>1.799276958172506</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.248897347711576</v>
+        <v>2.261940244005942</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.833585118042606</v>
+        <v>1.846651372343082</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.696980231657797</v>
+        <v>1.710161240953035</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.635980345475495</v>
+        <v>1.649179084430259</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.2899873918525202</v>
+        <v>0.3033925195053513</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.076969604725029</v>
+        <v>1.090426898435247</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.9460635058721181</v>
+        <v>0.9595157945922281</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.02994112633216872</v>
+        <v>0.04349717268377162</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.373230103375015</v>
+        <v>-1.383659739073167</v>
       </c>
     </row>
     <row r="24">
@@ -3153,98 +3153,98 @@
         <v>549</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.33351978543665</v>
+        <v>2.346042075112273</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.364933422017025</v>
+        <v>4.377843231593076</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.695019178079818</v>
+        <v>2.70802630949742</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.825272310687318</v>
+        <v>2.838251453085782</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.651149820569607</v>
+        <v>2.664260624944546</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.6771892081942</v>
+        <v>3.690232104488565</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.863858041012989</v>
+        <v>2.876924295313465</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.214525279754255</v>
+        <v>2.227706289049493</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.153525393571954</v>
+        <v>2.166724132526717</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7569521211123345</v>
+        <v>0.7703572487651655</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.645094971658139</v>
+        <v>1.658552265368357</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.315179404049111</v>
+        <v>1.328631692769221</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5306260681497506</v>
+        <v>0.5441821145013535</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.676847499391819</v>
+        <v>-0.6872771350899711</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.4356</t>
+          <t>X &gt; 0.4357</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>509</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.712848516725195</v>
+        <v>2.725370806400818</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.441157025568394</v>
+        <v>4.454066835144445</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.260433702075943</v>
+        <v>3.273440833493545</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.37300510580328</v>
+        <v>4.385984248201744</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.638120236507135</v>
+        <v>3.651231040882074</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.721416791118671</v>
+        <v>4.734459687413036</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.850828456950516</v>
+        <v>3.863894711250992</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.187181403945054</v>
+        <v>3.200362413240292</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.51910882621069</v>
+        <v>3.532307565165453</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.883129024286887</v>
+        <v>1.896534151939719</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.464230316865184</v>
+        <v>2.477687610575401</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.909222511538708</v>
+        <v>1.922674800258818</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.292504246369838</v>
+        <v>1.30606029272144</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.2259473093695874</v>
+        <v>-0.2363769450677395</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>469</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.517222660600261</v>
+        <v>2.529744950275884</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.530382523115748</v>
+        <v>4.543292332691799</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.495854967905082</v>
+        <v>3.508862099322684</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.692206181536037</v>
+        <v>4.705185323934501</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.153784966463867</v>
+        <v>4.166895770838806</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.090885752793596</v>
+        <v>5.103928649087962</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.366493186907249</v>
+        <v>4.379559441207725</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.259650939511673</v>
+        <v>3.27283194880691</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.411870669534068</v>
+        <v>3.425069408488831</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.135306252096761</v>
+        <v>2.148711379749592</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.78343139259794</v>
+        <v>2.796888686308158</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.178155701329295</v>
+        <v>2.191607990049405</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.757901090384394</v>
+        <v>1.771457136735997</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.3018654930231577</v>
+        <v>0.2914358573250055</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>408</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.428130307241005</v>
+        <v>1.440652596916628</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.512635125649297</v>
+        <v>2.525544935225348</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.627570340621332</v>
+        <v>1.640577472038935</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.983313669307265</v>
+        <v>2.996292811705729</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.199794415019404</v>
+        <v>2.212905219394344</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.232530470382137</v>
+        <v>3.245573366676503</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.167404596247103</v>
+        <v>2.180470850547579</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9649270798185441</v>
+        <v>0.9781080891137819</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.9039271936362425</v>
+        <v>0.9171259325910057</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4363940698230522</v>
+        <v>-0.4229889421702211</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.3392447627221102</v>
+        <v>0.352702056432328</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.096960315226575</v>
+        <v>-1.083508026506465</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-2.007411004602858</v>
+        <v>-1.993854958251255</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.963572025267737</v>
+        <v>-3.974001660965889</v>
       </c>
     </row>
     <row r="28">
@@ -3361,46 +3361,46 @@
         <v>357</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4477381503782638</v>
+        <v>0.4602604400538866</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.637284985593276</v>
+        <v>1.650194795169327</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1581439450929523</v>
+        <v>-0.1451368136753501</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8124453219683332</v>
+        <v>0.8254244643667974</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2861999827396957</v>
+        <v>-0.2730891783647564</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.8515780894297507</v>
+        <v>0.8646209857241161</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2066202825216195</v>
+        <v>0.2196865368220955</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.661123340349519</v>
+        <v>-1.647942331054281</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.442011181713895</v>
+        <v>-1.428812442759131</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.572248411559748</v>
+        <v>-2.558843283906917</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.936665601423549</v>
+        <v>-1.923208307713331</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.423290847439453</v>
+        <v>-4.409838558719343</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.843545458384355</v>
+        <v>-4.829989412032752</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.834720484651491</v>
+        <v>-6.845150120349643</v>
       </c>
     </row>
     <row r="29">
@@ -3413,46 +3413,46 @@
         <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.020252200336159</v>
+        <v>-2.007729910660537</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.4772516808083012</v>
+        <v>-0.46434187123225</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.764864866900162</v>
+        <v>-2.75185773548256</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.057324668046604</v>
+        <v>-1.04434552564814</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.911203296367979</v>
+        <v>-1.89809249199304</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9828465321538999</v>
+        <v>-0.9698036358595346</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.698495075924598</v>
+        <v>-1.685428821624122</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.058422954201369</v>
+        <v>-4.045241944906131</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.488508013885252</v>
+        <v>-3.475309274930488</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.338633198913179</v>
+        <v>-4.325228071260348</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.281556870233906</v>
+        <v>-3.268099576523689</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.770833018882172</v>
+        <v>-5.757380730162062</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.875630216577868</v>
+        <v>-5.862074170226265</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-7.834110777046057</v>
+        <v>-7.844540412744209</v>
       </c>
     </row>
     <row r="30">
@@ -3465,46 +3465,46 @@
         <v>257</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.244411082855891</v>
+        <v>-4.231888793180268</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.132249287259839</v>
+        <v>-3.119339477683788</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.083538227319458</v>
+        <v>-5.070531095901856</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.396864861248929</v>
+        <v>-3.383885718850465</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.935286076321098</v>
+        <v>-3.922175271946159</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.859634021873909</v>
+        <v>-2.846591125579543</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.500787972609231</v>
+        <v>-4.487721718308755</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-6.913496663219526</v>
+        <v>-6.900315653924288</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.58539149103607</v>
+        <v>-6.572192752081307</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.435516676063997</v>
+        <v>-7.422111548411166</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.08384976691854</v>
+        <v>-6.070392473208322</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.994991901401903</v>
+        <v>-7.981539612681793</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-8.804351570712562</v>
+        <v>-8.790795524360959</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.11105047189931</v>
+        <v>-10.12148010759746</v>
       </c>
     </row>
     <row r="31">
@@ -3517,46 +3517,46 @@
         <v>182</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.295636122407771</v>
+        <v>-0.2831138327321483</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.357759185921481</v>
+        <v>-1.344849376345429</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.400979540869727</v>
+        <v>-3.387972409452125</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.721275858811666</v>
+        <v>-2.708296716413201</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.457499271686039</v>
+        <v>-5.4443884673111</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.962255136168174</v>
+        <v>-2.949212239873809</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-5.794241600693212</v>
+        <v>-5.781175346392736</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.45922719727691</v>
+        <v>-8.446046187981672</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-7.970776534008664</v>
+        <v>-7.957577795053901</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.820901719036591</v>
+        <v>-8.80749659138376</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.827852845551966</v>
+        <v>-6.814395551841748</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-8.441821336558185</v>
+        <v>-8.428369047838075</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-9.411526496953641</v>
+        <v>-9.397970450602038</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-11.9090579119301</v>
+        <v>-11.91948754762825</v>
       </c>
     </row>
     <row r="32">
@@ -3569,46 +3569,46 @@
         <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6100099556520888</v>
+        <v>0.6225322453277116</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.067401859929213</v>
+        <v>1.080311669505264</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.741498670574011</v>
+        <v>2.754505801991613</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.561406975595304</v>
+        <v>3.574386117993768</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4252901015458406</v>
+        <v>-0.4121792971709013</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.251462180997407</v>
+        <v>1.264505077291773</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.591892225930046</v>
+        <v>-1.57882597162957</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.12804114195292</v>
+        <v>-4.114860132657682</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.189041028135222</v>
+        <v>-4.175842289180459</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.659855868335562</v>
+        <v>-3.646450740682731</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.174954020239355</v>
+        <v>-3.161496726529137</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.209536380135297</v>
+        <v>-5.196084091415187</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-7.009101335907786</v>
+        <v>-6.995545289556183</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-10.20765586570047</v>
+        <v>-10.21808550139862</v>
       </c>
     </row>
     <row r="33">
@@ -3621,46 +3621,46 @@
         <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9309383202099752</v>
+        <v>-0.9184160305343525</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.9800119331742323</v>
+        <v>-0.9671021235981812</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.750119360229178</v>
+        <v>1.76312649164678</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.880372492836678</v>
+        <v>1.893351635235142</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.345548722235492</v>
+        <v>-3.332437917860553</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.7043567845198311</v>
+        <v>-0.6913138882254657</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.91409050179211</v>
+        <v>-3.901024247491634</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.943773900573611</v>
+        <v>-5.930592891278373</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.51114897178384</v>
+        <v>-4.497743844131008</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.715902296101419</v>
+        <v>-4.702445002391201</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-7.025269138755988</v>
+        <v>-7.011816850035878</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-9.008023749700889</v>
+        <v>-8.994467703349287</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.4458024174246</v>
+        <v>-13.45623205312275</v>
       </c>
     </row>
     <row r="34">
@@ -3673,46 +3673,46 @@
         <v>111</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2411860679577273</v>
+        <v>-0.2286637782821046</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.753660581822885</v>
+        <v>-2.740750772246834</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.445826585716766</v>
+        <v>-0.4328194542991639</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.216474354010167</v>
+        <v>-1.203495211611703</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.16030097448774</v>
+        <v>-7.1471901701128</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.160156334069384</v>
+        <v>-4.147113437775019</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.749394555846159</v>
+        <v>-8.736328301545683</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-11.01837975642947</v>
+        <v>-11.00519874713423</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.07937964261177</v>
+        <v>-11.06618090365701</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-10.12770302583789</v>
+        <v>-10.11429789818506</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-9.431555449254574</v>
+        <v>-9.418098155544357</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.29807319281004</v>
+        <v>-10.28462090408993</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-11.61922870465585</v>
+        <v>-11.60567265830424</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-15.87401187688406</v>
+        <v>-15.88444151258221</v>
       </c>
     </row>
     <row r="35">
@@ -3725,46 +3725,46 @@
         <v>80</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.993438320209975</v>
+        <v>-4.980916030534353</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-9.105011933174232</v>
+        <v>-9.092102123598181</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-5.749880639770822</v>
+        <v>-5.73687350835322</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.619627507163322</v>
+        <v>-5.606648364764858</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-16.15804872223549</v>
+        <v>-16.14493791786055</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-14.61060678451983</v>
+        <v>-14.59756388822547</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-18.44534050179211</v>
+        <v>-18.43227424749163</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-22.66252390057361</v>
+        <v>-22.64934289127837</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-22.72352378675591</v>
+        <v>-22.71032504780115</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-19.82364897178384</v>
+        <v>-19.81024384413101</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-20.02840229610142</v>
+        <v>-20.0149450023912</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-19.99401913875599</v>
+        <v>-19.98056685003588</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-20.41427374970089</v>
+        <v>-20.40071770334929</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-23.9145524174246</v>
+        <v>-23.92498205312275</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that MA Cross-50-200 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that MA Cross-50-200 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3911,46 +3911,46 @@
         <v>80</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.743438320209975</v>
+        <v>-8.730916030534353</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.605011933174232</v>
+        <v>-6.592102123598181</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.999880639770822</v>
+        <v>-6.98687350835322</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.119627507163322</v>
+        <v>-8.106648364764858</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.408048722235492</v>
+        <v>-7.394937917860553</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.610606784519831</v>
+        <v>-9.597563888225466</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.19534050179211</v>
+        <v>-12.18227424749163</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-11.41252390057361</v>
+        <v>-11.39934289127837</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.223523786755912</v>
+        <v>-5.210325047801149</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.823648971783847</v>
+        <v>-4.810243844131016</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.778402296101419</v>
+        <v>-3.764945002391201</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.994019138755995</v>
+        <v>-4.980566850035885</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.914273749700889</v>
+        <v>-7.900717703349287</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-5.164552417424609</v>
+        <v>-5.174982053122761</v>
       </c>
     </row>
     <row r="7">
@@ -3963,98 +3963,98 @@
         <v>135</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.826771653543311</v>
+        <v>-5.814249363867688</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.216123044285347</v>
+        <v>-5.203213234709295</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.09247323236341</v>
+        <v>-7.079466100945808</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.702960840496658</v>
+        <v>-7.689981698098194</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.241382055568828</v>
+        <v>-8.228271251193888</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.64764382155687</v>
+        <v>-11.6346009252625</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.47311827956989</v>
+        <v>-12.46005202526941</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.495857233906946</v>
+        <v>-8.482676224611708</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.630931194163324</v>
+        <v>-2.617732455208561</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.999574897709763</v>
+        <v>-1.986169770056932</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7586347409356193</v>
+        <v>0.7720920346458371</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.6750112944803206</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.330940416367554</v>
+        <v>-3.317384370015951</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.340478343350526</v>
+        <v>-2.350907979048678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.2402</t>
+          <t>X &lt; -0.2401</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>254</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.887139107611546</v>
+        <v>-2.874616817935923</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.317610358371084</v>
+        <v>-3.304700548795033</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.975926719761752</v>
+        <v>-3.962947577363288</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.333245572629195</v>
+        <v>-3.320134768254256</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.823205209716683</v>
+        <v>-3.810162313422317</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.514238139587384</v>
+        <v>-3.501171885286908</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.194019963565744</v>
+        <v>-3.180838954270506</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4991143379370087</v>
+        <v>-0.4859155989822455</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.012965201444509</v>
+        <v>1.02637032909734</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.595613451930078</v>
+        <v>1.609070745640295</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.629996609275508</v>
+        <v>1.643448897995619</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.02863963612588094</v>
+        <v>0.04219568247748384</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.640565692811613</v>
+        <v>2.630136057113461</v>
       </c>
     </row>
     <row r="9">
@@ -4067,98 +4067,98 @@
         <v>373</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3215750846157661</v>
+        <v>0.3340973742913889</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.122870104359286</v>
+        <v>1.135779913935338</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1918083682720777</v>
+        <v>0.2048154996896798</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8582545303701963</v>
+        <v>0.8712336727686605</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3198333152980268</v>
+        <v>0.3329441196729661</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3491787382683782</v>
+        <v>0.3622216345627436</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.06873456523202</v>
+        <v>1.081800819532496</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.942033740177067</v>
+        <v>1.955214749472304</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.4896129424666</v>
+        <v>3.502811681421363</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.588549419637069</v>
+        <v>5.6019545472899</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.45618215430072</v>
+        <v>6.469639448010938</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.954372282155539</v>
+        <v>5.967824570875649</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.193635097484091</v>
+        <v>4.207191143835693</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.979549459250997</v>
+        <v>4.969119823552845</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1607</t>
+          <t>X &lt; -0.1606</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>589</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.238769389819488</v>
+        <v>-2.226247100143866</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.152550133513792</v>
+        <v>-2.139640323937741</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.377639553183386</v>
+        <v>-2.364632421765783</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3798142643789433</v>
+        <v>-0.3668351219804791</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.59735262715909</v>
+        <v>-1.584241822784151</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.809248550224417</v>
+        <v>-1.796205653930052</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.554423693642704</v>
+        <v>-1.541357439342228</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3238142231542582</v>
+        <v>-0.3106332138590204</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.652537333787386</v>
+        <v>1.665736072742149</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.349101452664371</v>
+        <v>3.362506580317202</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.144348128346792</v>
+        <v>3.15780542205701</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.839172711838245</v>
+        <v>2.852625000558355</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.909580240112348</v>
+        <v>1.923136286463951</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.819742998534657</v>
+        <v>1.809313362836505</v>
       </c>
     </row>
     <row r="11">
@@ -4171,306 +4171,306 @@
         <v>860</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.330647622535551</v>
+        <v>-1.318125332859928</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.54687239829051</v>
+        <v>-1.533962588714459</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.058020174654544</v>
+        <v>-2.045013043236942</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.06730192576797123</v>
+        <v>-0.05432278336950702</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.303397559444797</v>
+        <v>-1.290286755069857</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.35479283103146</v>
+        <v>-1.341749934737095</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.9046428273735</v>
+        <v>-1.891576573073024</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7439192494108156</v>
+        <v>-0.7307382401155778</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4741506318487367</v>
+        <v>0.4873493708034999</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.368211493332439</v>
+        <v>1.38161662098527</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.512295378317184</v>
+        <v>1.525752672027402</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5001669077556343</v>
+        <v>0.5136191964757444</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.03636677295669699</v>
+        <v>-0.02281072660509409</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.01920358021529722</v>
+        <v>-0.02963321591344936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.08116</t>
+          <t>X &lt; -0.08113</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>1065</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.507522827252231</v>
+        <v>-1.495000537576608</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.555716158526344</v>
+        <v>-2.542806348950293</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.420068433198047</v>
+        <v>-3.407061301780445</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.693571169135154</v>
+        <v>-1.68059202673669</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.795372665897467</v>
+        <v>-2.782261861522528</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.497930728181807</v>
+        <v>-2.484887831887441</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.521631581604325</v>
+        <v>-3.508565327303849</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.862054417005531</v>
+        <v>-2.848873407710293</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.359674021497689</v>
+        <v>-2.346475282542926</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.176935356760367</v>
+        <v>-2.163530229107536</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.663378821923018</v>
+        <v>-2.649921528212801</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.474066087112796</v>
+        <v>-3.460613798392686</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.706527270827657</v>
+        <v>-3.692971224476054</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.362909224936338</v>
+        <v>-3.37333886063449</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.04141</t>
+          <t>X &lt; -0.04138</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>1252</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.7529319910960552</v>
+        <v>-0.781311287451345</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.056714229294577</v>
+        <v>-1.085773009674128</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.568026440087777</v>
+        <v>-1.596928931947843</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.0476608140626098</v>
+        <v>-0.07772601928149925</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.7810645952513653</v>
+        <v>-0.8108776482332729</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.8377712007231679</v>
+        <v>-0.8674051580667381</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.91314654312756</v>
+        <v>-1.942004191891954</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.542794385856027</v>
+        <v>-1.572236372995384</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.083396398220884</v>
+        <v>-1.113268564109816</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9342067407081416</v>
+        <v>-0.9647024428571243</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.493713300886107</v>
+        <v>-1.523909145817498</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.293500383767956</v>
+        <v>-2.32307083727671</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.590791321585876</v>
+        <v>-2.620390488664526</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.261197784836746</v>
+        <v>-2.271627420534898</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.001654</t>
+          <t>X &lt; -0.001627</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7881177199371194</v>
+        <v>-0.8108410475759413</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.7261723427305498</v>
+        <v>-0.7496737470633903</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.084580093322735</v>
+        <v>-1.108033917909538</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.02923106150372234</v>
+        <v>-0.05336967624026556</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3936848371465658</v>
+        <v>-0.41783607233765</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2642686599476178</v>
+        <v>-0.2883983615496817</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9282172141208704</v>
+        <v>-0.9519525500241457</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8102278073590767</v>
+        <v>-0.8342743981276826</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2166650761935003</v>
+        <v>-0.2411680909814038</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.4122810213527472</v>
+        <v>0.3869440845383991</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3718088895080101</v>
+        <v>-0.3967226276485718</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4364590012989424</v>
+        <v>-0.4613360808051041</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.336900984914088</v>
+        <v>-0.3620579095348546</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3237058929923862</v>
+        <v>-0.3039366611007495</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.0381</t>
+          <t>X &lt; 0.03813</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1634</v>
+        <v>1635</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.127318101630742</v>
+        <v>-1.145964574223669</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.492618251521741</v>
+        <v>-1.511652821837401</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.490762098737385</v>
+        <v>-1.509959778098057</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4766834682338867</v>
+        <v>-0.4964659939441916</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6779817715355492</v>
+        <v>-0.6978576258897533</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.5911183557743982</v>
+        <v>-0.6109540282132997</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.947625693748229</v>
+        <v>-0.9672925178935827</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.8942312176467766</v>
+        <v>-0.9141204659279794</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1289539270853837</v>
+        <v>-0.14934943804505</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.2755573774225084</v>
+        <v>0.2545822693528237</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.07803577197191203</v>
+        <v>-0.09888883633503553</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.05182438202641038</v>
+        <v>0.03088702901116136</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.2164601952532408</v>
+        <v>0.1952480668218612</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5621917686219078</v>
+        <v>0.5780760508527791</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.07786</t>
+          <t>X &lt; 0.07788</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8514891676676015</v>
+        <v>-0.8663051252934864</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.269823803868455</v>
+        <v>-1.284898733767676</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.159477670523742</v>
+        <v>-1.174737843276375</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1521208758635808</v>
+        <v>-0.1678890858677207</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.3963714398575675</v>
+        <v>-0.4121792971709013</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.547940825943094</v>
+        <v>-0.5635936122169767</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.9227581425997684</v>
+        <v>-0.9382487562542465</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.201864676756493</v>
+        <v>-1.21735564366945</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6490557016495231</v>
+        <v>-0.6648705023466093</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.1928613187769272</v>
+        <v>-0.2091800143437794</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6340998466871426</v>
+        <v>-0.6502563382081235</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6233478547922147</v>
+        <v>-0.6395125369368344</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4809048797648572</v>
+        <v>-0.4972813687728319</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3612190840912675</v>
+        <v>-0.3482229912890631</v>
       </c>
     </row>
     <row r="17">
@@ -4480,49 +4480,49 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4380317071626152</v>
+        <v>-0.4487588174928092</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.355794230894396</v>
+        <v>-1.366454223687548</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.8326176701822732</v>
+        <v>-0.8436012687465961</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3204105049261869</v>
+        <v>-0.3316036420457209</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4317729836499922</v>
+        <v>-0.4430363518650253</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5129802731002115</v>
+        <v>-0.5241529661126663</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6630824372759818</v>
+        <v>-0.6742133428789998</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.061224035042464</v>
+        <v>-1.072281959378728</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3356314100742992</v>
+        <v>-0.3470350433188614</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.005310202733880942</v>
+        <v>-0.006432184938191199</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.4884561560655101</v>
+        <v>-0.5000279992507757</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2045040960977076</v>
+        <v>-0.2162041929443106</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1191943545219303</v>
+        <v>0.1072526603687152</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.3944363466203384</v>
+        <v>0.4034096809293573</v>
       </c>
     </row>
     <row r="18">
@@ -4532,49 +4532,49 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3734383202099778</v>
+        <v>-0.3817556946686977</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8036914049629473</v>
+        <v>-0.8121021235981729</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.05632579589572373</v>
+        <v>-0.0651048008702233</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2559231536296309</v>
+        <v>0.2470345815922315</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2201564059696395</v>
+        <v>0.2111894349628329</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.0587318928348779</v>
+        <v>0.04987200921042501</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3166883674941801</v>
+        <v>0.3077057124282092</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2086530622262401</v>
+        <v>-0.2175064839006637</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3944537413339759</v>
+        <v>0.3853428222349535</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.851280775305689</v>
+        <v>0.8418428332365693</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2677824428543971</v>
+        <v>0.2585395419684886</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.4052375908542984</v>
+        <v>0.3959391740605156</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8919963467621344</v>
+        <v>0.8824281383542072</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.044233268140339</v>
+        <v>1.050902191250231</v>
       </c>
     </row>
     <row r="19">
@@ -4584,49 +4584,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2661</v>
+        <v>2663</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.36180032469764</v>
+        <v>-0.3882403952578244</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7941252889542554</v>
+        <v>-0.8210740862150061</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3082638733037584</v>
+        <v>-0.3357889907765568</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1577218538499565</v>
+        <v>-0.1853053045329105</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2264007821605816</v>
+        <v>-0.2542193549863043</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2456760988697724</v>
+        <v>-0.2733407508237491</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.02729817886756081</v>
+        <v>-0.0006263074167236482</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2693855428683278</v>
+        <v>-0.297338395212428</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1403171734841493</v>
+        <v>0.1494950421538732</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6242872383474918</v>
+        <v>0.6326695416957619</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.02790401020489242</v>
+        <v>0.03663039145725833</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.308740906305971</v>
+        <v>0.2797520993074656</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6234798190444124</v>
+        <v>0.6315645789329949</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6692506641236875</v>
+        <v>0.6910524943800596</v>
       </c>
     </row>
     <row r="20">
@@ -4636,49 +4636,49 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2845</v>
+        <v>2846</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1841311123723202</v>
+        <v>-0.1899051875822764</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5173325492050296</v>
+        <v>-0.5231728023945408</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.01692608291824627</v>
+        <v>0.01085137789109325</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.09622187987695696</v>
+        <v>0.0901303467197323</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.03238575569022117</v>
+        <v>0.02625297530932613</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1766775871836899</v>
+        <v>-0.1827075462492971</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1020726196041721</v>
+        <v>-0.1081417553780639</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.4448809682691532</v>
+        <v>-0.4508856682769675</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.03054133061556286</v>
+        <v>-0.03670175772749218</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.4023075041726401</v>
+        <v>0.3958965067461833</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1471595016513945</v>
+        <v>0.1408114033651984</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3067360421361798</v>
+        <v>0.3003320263686149</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6090923781979143</v>
+        <v>0.6025313307216678</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8086461765999999</v>
+        <v>0.8132470403417571</v>
       </c>
     </row>
     <row r="21">
@@ -4688,49 +4688,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3056</v>
+        <v>3057</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1621498192491302</v>
+        <v>0.1575204515503401</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.03069641818075297</v>
+        <v>-0.03540613141831983</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6354307394270933</v>
+        <v>0.6304667784785991</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.7184351151458728</v>
+        <v>0.713452711205143</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6873835779276334</v>
+        <v>0.6823614950552965</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.611325330362682</v>
+        <v>0.606351283063276</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7078589758441893</v>
+        <v>0.7028432459809437</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5200365174538248</v>
+        <v>0.5150384342195053</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8365872880562435</v>
+        <v>0.8314776955038781</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.083213773314199</v>
+        <v>1.077946289812147</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8317644250492862</v>
+        <v>0.8265582655826549</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.015627689236162</v>
+        <v>1.010361557940591</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.333763541761336</v>
+        <v>1.328353585074524</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.733353341737697</v>
+        <v>1.736614283154644</v>
       </c>
     </row>
     <row r="22">
@@ -4740,101 +4740,101 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3239</v>
+        <v>3240</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2179155649824196</v>
+        <v>-0.2214632177461553</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3061808042908112</v>
+        <v>-0.3098143007199567</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2385808986907136</v>
+        <v>0.2347506073034964</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2625670142278764</v>
+        <v>0.258736250619755</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1104241841684441</v>
+        <v>0.1066010171963825</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1476315893637548</v>
+        <v>0.1438154221193599</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1721887649977845</v>
+        <v>0.1683571045256116</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.09318645835480766</v>
+        <v>-0.09697074093948999</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2635292342058619</v>
+        <v>0.2596287272373701</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4480901586509418</v>
+        <v>0.4440718155483978</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3224613683032658</v>
+        <v>0.3184654200571515</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3743085378870248</v>
+        <v>0.3702968143688068</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6814052626447875</v>
+        <v>0.6772674864069614</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9179576165365049</v>
+        <v>0.9206969592229228</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.3561</t>
+          <t>X &lt; 0.3562</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3374</v>
+        <v>3375</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1462283999265424</v>
+        <v>-0.1491568805933809</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4724070897011146</v>
+        <v>-0.4753321206457173</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1424212601548618</v>
+        <v>-0.1454677198121672</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.003894951465518659</v>
+        <v>0.000811014851102243</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1932985005387735</v>
+        <v>-0.1963563575768674</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2936345787244434</v>
+        <v>-0.2966475417873866</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3918799871514764</v>
+        <v>-0.3948703444756703</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5767250840055667</v>
+        <v>-0.5796889427424361</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.4144086639385165</v>
+        <v>-0.417425639517127</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.2121924886577276</v>
+        <v>-0.215319310245242</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3411799093676322</v>
+        <v>-0.3442818881224028</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2013651103199621</v>
+        <v>-0.2045082181140501</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.07646699103984389</v>
+        <v>0.07321594593981473</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2837285547152888</v>
+        <v>0.2861290579883544</v>
       </c>
     </row>
     <row r="24">
@@ -4844,101 +4844,101 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3430</v>
+        <v>3431</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2424943759752907</v>
+        <v>-0.2451436728107765</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6186667850045637</v>
+        <v>-0.6212917837782541</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.27145866941337</v>
+        <v>-0.2742064543148643</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1545112280935612</v>
+        <v>-0.1572877137913125</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.2991507867891343</v>
+        <v>-0.3019146620465989</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.480298465729831</v>
+        <v>-0.4829956997985931</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.5201877523012683</v>
+        <v>-0.5228792504002939</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6223609203640592</v>
+        <v>-0.6250484484503218</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.463698459245002</v>
+        <v>-0.4664368056591215</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2786577079515808</v>
+        <v>-0.2814956636361003</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4089004027137122</v>
+        <v>-0.4117126203294674</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.2416881364249832</v>
+        <v>-0.244548790030052</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.004407821400100431</v>
+        <v>-0.007361059992639696</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.1452143464237921</v>
+        <v>0.1474458104738616</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.4356</t>
+          <t>X &lt; 0.4357</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3470</v>
+        <v>3471</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2683450098453548</v>
+        <v>-0.270812701028035</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5725593197336778</v>
+        <v>-0.5750191491508616</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.3200472585585246</v>
+        <v>-0.322600102264758</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3466390014161931</v>
+        <v>-0.3491792466953427</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4096296362912568</v>
+        <v>-0.4121792971709013</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.585304886877509</v>
+        <v>-0.5877909649716599</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6257402717087075</v>
+        <v>-0.6282201934375777</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7321441537381688</v>
+        <v>-0.7346175533433765</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6335957292019501</v>
+        <v>-0.6361018026918259</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4317376303906357</v>
+        <v>-0.4343445635554701</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5052954720300136</v>
+        <v>-0.5078926132144588</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3108394152536889</v>
+        <v>-0.3134922747407458</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1099666335960165</v>
+        <v>-0.1126992701695571</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.06959743848317856</v>
+        <v>0.07170478064273311</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3510</v>
+        <v>3511</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2084539319045504</v>
+        <v>-0.2107684709429805</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.5274991563428841</v>
+        <v>-0.529797269780417</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.3107298303416783</v>
+        <v>-0.3131086020499865</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3355365980724159</v>
+        <v>-0.3379036899565619</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.432345397427305</v>
+        <v>-0.4347106451332863</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.574222475253201</v>
+        <v>-0.5765351868898634</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6435918523749891</v>
+        <v>-0.6458899382250038</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6972224216202534</v>
+        <v>-0.6995277078834405</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5720301878938869</v>
+        <v>-0.5743751046839662</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4390445323985261</v>
+        <v>-0.4414671727227528</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5140982824378852</v>
+        <v>-0.5165101702910349</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3214678859086035</v>
+        <v>-0.3239343422078065</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.1561564042152668</v>
+        <v>-0.1586903684973535</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.004296007168193228</v>
+        <v>-0.002310449590993358</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3571</v>
+        <v>3572</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.03808117735283645</v>
+        <v>-0.04019078646182805</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.211626501971331</v>
+        <v>-0.213753909312473</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.03310230364575517</v>
+        <v>-0.03529661747965207</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05519019914880374</v>
+        <v>-0.05737421624447592</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1315124093863247</v>
+        <v>-0.1336980407312538</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2658177372999333</v>
+        <v>-0.2679549496779714</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3074142860291147</v>
+        <v>-0.3095444346947644</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3680033526284063</v>
+        <v>-0.3701366307976528</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.217930945592606</v>
+        <v>-0.2201097836132817</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1016209997558661</v>
+        <v>-0.1038680052048306</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1787940140644935</v>
+        <v>-0.1810289184751142</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.0951916085152078</v>
+        <v>0.09288026803911009</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3066109087537541</v>
+        <v>0.3042221231270616</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.4882759219761255</v>
+        <v>0.4899115638985236</v>
       </c>
     </row>
     <row r="28">
@@ -5052,49 +5052,49 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3622</v>
+        <v>3623</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.07877626025770468</v>
+        <v>0.0768397450432019</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.0874004857333901</v>
+        <v>-0.08935109196131918</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1656850084537922</v>
+        <v>0.1636493314926852</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.2008570743344791</v>
+        <v>0.1988154392538632</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1456554914797366</v>
+        <v>0.1436083376460502</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.01749238903389028</v>
+        <v>0.01549036680069804</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.07974391871137243</v>
+        <v>-0.08172328330429934</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.09085907146666017</v>
+        <v>-0.09285350026156891</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.02875082035740206</v>
+        <v>0.02672015616797552</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1039572058223399</v>
+        <v>0.1018736083090204</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.05263218665720615</v>
+        <v>0.05055417025082676</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4060912365199556</v>
+        <v>0.403915908584807</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.5535015746159786</v>
+        <v>0.5512690516175951</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.7085839713109081</v>
+        <v>0.7099889653702078</v>
       </c>
     </row>
     <row r="29">
@@ -5104,49 +5104,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3662</v>
+        <v>3663</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2956773260485264</v>
+        <v>0.2938391381272396</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1138231239841758</v>
+        <v>0.1119795090548763</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3871327008226899</v>
+        <v>0.3852005253974653</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3689345843399536</v>
+        <v>0.3670107694578419</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.281272988470036</v>
+        <v>0.2793540211372658</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1850335424556491</v>
+        <v>0.1831498137630945</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.08797920384975555</v>
+        <v>0.08611812308057409</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.09919910924099895</v>
+        <v>0.09731832431170062</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.189620472856852</v>
+        <v>0.1877120296252386</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2274966910639549</v>
+        <v>0.2255483565780168</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.1472457257266839</v>
+        <v>0.1453114078652078</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4699546603706466</v>
+        <v>0.4679324678358867</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.583883498456359</v>
+        <v>0.5818150477424169</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.712700449861039</v>
+        <v>0.7139750858343845</v>
       </c>
     </row>
     <row r="30">
@@ -5156,49 +5156,49 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3722</v>
+        <v>3723</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.4115148257070231</v>
+        <v>0.4098762606862039</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.28706091096074</v>
+        <v>0.2854079165624555</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4961011443170449</v>
+        <v>0.4943798392632814</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.5071141862986295</v>
+        <v>0.5053928889185144</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3854382785685857</v>
+        <v>0.3837330360515594</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2955594353193192</v>
+        <v>0.2938861251757672</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2523666583044246</v>
+        <v>0.2507016238220388</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2291070007139453</v>
+        <v>0.2274337244363025</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3439567606012162</v>
+        <v>0.3422500594949938</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3675748607443339</v>
+        <v>0.3658361129390215</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2853560931603241</v>
+        <v>0.2836325606791092</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.5228981544770974</v>
+        <v>0.5211110023131127</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6819524119966687</v>
+        <v>0.6801093643198897</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.7321429076694272</v>
+        <v>0.7332236949298974</v>
       </c>
     </row>
     <row r="31">
@@ -5208,49 +5208,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3797</v>
+        <v>3798</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1312335958005235</v>
+        <v>0.129947259940586</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1349460610499733</v>
+        <v>0.1336196611787202</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3057916291367491</v>
+        <v>0.3044102931694823</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3979059837744288</v>
+        <v>0.3965028957393457</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.3730863276856908</v>
+        <v>0.371676214001802</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2382762641004064</v>
+        <v>0.2369079982695439</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2205375213414342</v>
+        <v>0.2191712189998256</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1622197228815523</v>
+        <v>0.1608568984166823</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2735829991462495</v>
+        <v>0.2721887570897294</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.279942188437154</v>
+        <v>0.2785252247800898</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.1952819144249034</v>
+        <v>0.19388162218128</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3761440620863326</v>
+        <v>0.3746963078588621</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.5237199311837841</v>
+        <v>0.5222225440842507</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.6041465554487147</v>
+        <v>0.6050337446655618</v>
       </c>
     </row>
     <row r="32">
@@ -5260,49 +5260,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3834</v>
+        <v>3835</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.09299266497328773</v>
+        <v>0.0918490422307201</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.02915343344042753</v>
+        <v>0.0279914558143517</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.03848086868171663</v>
+        <v>0.03730745888547204</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.130892784199844</v>
+        <v>0.1296975390062656</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1270800833851098</v>
+        <v>0.1258737366659801</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.04842496977480693</v>
+        <v>0.0472448549439406</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.003956556265684696</v>
+        <v>0.002785617162196274</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.08439890057361055</v>
+        <v>-0.08555741874517508</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.05128736198073369</v>
+        <v>0.05009161886551539</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.002778726864612224</v>
+        <v>-0.003979191877810706</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.01048465210871541</v>
+        <v>-0.0116880977533711</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.168910996801884</v>
+        <v>0.1676609320855675</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3370300312639074</v>
+        <v>0.3357265093723001</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4190417401132152</v>
+        <v>0.4198680120662885</v>
       </c>
     </row>
     <row r="33">
@@ -5312,49 +5312,49 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3851</v>
+        <v>3852</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.146313232585058</v>
+        <v>0.145215922893847</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.101563267447041</v>
+        <v>0.1004444602527528</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.08323691589981053</v>
+        <v>0.0821143249369598</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2017270641912461</v>
+        <v>0.2005758713822132</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2214849565209889</v>
+        <v>0.2203171973945572</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.1185976725934168</v>
+        <v>0.117462018510281</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.07397002179524748</v>
+        <v>0.07284365870168585</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.04196387983210315</v>
+        <v>-0.04307021113321952</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.06693264477936367</v>
+        <v>0.06579629002617082</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.009360107334188683</v>
+        <v>0.008220886159449492</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.02673522335888379</v>
+        <v>0.02558677452189784</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2055007159027156</v>
+        <v>0.2043060093310132</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3710325846708713</v>
+        <v>0.3697858004140144</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4797607479869797</v>
+        <v>0.4805215813528392</v>
       </c>
     </row>
     <row r="34">
@@ -5364,49 +5364,49 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3868</v>
+        <v>3869</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1218670134669111</v>
+        <v>0.120835643860282</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1475653864133903</v>
+        <v>0.1464961758091903</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1533805100100523</v>
+        <v>0.1523017493787364</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.297726799180154</v>
+        <v>0.2966127850160163</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.315061930330927</v>
+        <v>0.3139326339702819</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.213954618988943</v>
+        <v>0.2128565399406384</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.1949820788530445</v>
+        <v>0.193886743220439</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.07753805089772925</v>
+        <v>0.07646356033453117</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.211539471700064</v>
+        <v>0.2104286951002479</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1505245819351657</v>
+        <v>0.1494127528222506</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1411275411499417</v>
+        <v>0.1400136752947461</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2676087682207609</v>
+        <v>0.2664623413875304</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.4047363304231695</v>
+        <v>0.4035458625421882</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.4882397232165516</v>
+        <v>0.4889491952618457</v>
       </c>
     </row>
     <row r="35">
@@ -5416,49 +5416,49 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3899</v>
+        <v>3900</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.2161731317327664</v>
+        <v>0.2152250376997387</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2544869162249057</v>
+        <v>0.2535011483854603</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2571526083110243</v>
+        <v>0.2561589641601998</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3758316895621903</v>
+        <v>0.3748094357466485</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.4399553719303242</v>
+        <v>0.4389070552783565</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3932324783417016</v>
+        <v>0.3922006972402485</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3225806451612954</v>
+        <v>0.3215650153698988</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2280010674161375</v>
+        <v>0.2270011947431314</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.3604926066867122</v>
+        <v>0.359457282544561</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.267626969799565</v>
+        <v>0.2666004181640744</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2823357869329257</v>
+        <v>0.2813014746777185</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3824868853404055</v>
+        <v>0.3814269992721719</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.4895724041452638</v>
+        <v>0.4884773748357958</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.5231239098387945</v>
+        <v>0.5237358955952018</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/ma/ma_cross_50_200.xlsx
+++ b/workspaces/btc_daily_14days/ma/ma_cross_50_200.xlsx
@@ -568,885 +568,885 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.2998</t>
+          <t>X ≈ -0.2995</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>55</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-1.565545098164655</v>
+        <v>-1.594695211610919</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-3.172478507371096</v>
+        <v>-3.173647387770053</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-7.192762777331076</v>
+        <v>-7.19293351668022</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-7.064440206375764</v>
+        <v>-5.251473069528231</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.417740146168192</v>
+        <v>-7.555395997634356</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-14.5666530957199</v>
+        <v>-12.72838504551311</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.84036351598883</v>
+        <v>-10.97759581004844</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-4.233650831685473</v>
+        <v>-2.369124109660845</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>1.151814733033213</v>
+        <v>3.040818965076014</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>2.119327155593417</v>
+        <v>4.034882118073376</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>7.365631320344711</v>
+        <v>7.465462520758585</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>5.584748463042942</v>
+        <v>5.708377884159269</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>3.348471805373386</v>
+        <v>3.497119105425696</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>1.756836128697081</v>
+        <v>1.928834888262088</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.26</t>
+          <t>X ≈ -0.2598</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.4597674255555901</v>
+        <v>-0.009008858147986132</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-1.14642620850065</v>
+        <v>-0.7566759941603181</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-1.540003228768754</v>
+        <v>-1.980012345984022</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.2659174647400278</v>
+        <v>-0.1885791663575063</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>2.243462224334529</v>
+        <v>1.816815718101878</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>5.056523525357136</v>
+        <v>4.584284695822554</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>6.650483329853706</v>
+        <v>6.188153752897762</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>2.829386152284087</v>
+        <v>2.396121439585244</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>1.929921465267377</v>
+        <v>1.52750910334602</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>4.439115334427591</v>
+        <v>4.034684541572027</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>2.556399002451791</v>
+        <v>2.166413722488059</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>4.271339459757094</v>
+        <v>3.891031753764707</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>3.852500363652766</v>
+        <v>3.497079161816288</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>8.28090029981842</v>
+        <v>7.91368337311058</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.2203</t>
+          <t>X ≈ -0.22</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>7.15828183393883</v>
+        <v>7.293882869931615</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10.57956577421308</v>
+        <v>10.82904353103205</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.18930833678858</v>
+        <v>11.29206116093403</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11.1601315504719</v>
+        <v>11.42474550354605</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>8.110880999961225</v>
+        <v>8.381455767594232</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>9.248262111611339</v>
+        <v>9.508718543471289</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10.84324992871511</v>
+        <v>11.15645857382587</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>12.89637944208875</v>
+        <v>13.25393566661194</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>11.99982398847035</v>
+        <v>12.36709299821546</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>15.3510647016856</v>
+        <v>15.81624137899942</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>16.8300974239806</v>
+        <v>17.32466154124594</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>15.18950387715881</v>
+        <v>15.6792496885053</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>13.09357095862762</v>
+        <v>13.57970397625341</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>9.961572568725607</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.1805</t>
+          <t>X ≈ -0.1802</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.621858708739872</v>
+        <v>-6.366686296980816</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-7.768470711402792</v>
+        <v>-7.491651829298739</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.779278896007469</v>
+        <v>-6.520304028248539</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-2.496869091338638</v>
+        <v>-2.295034855256809</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-4.881761186991184</v>
+        <v>-4.605687713696121</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-5.510339922797101</v>
+        <v>-5.246050434284719</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-6.059010726737725</v>
+        <v>-5.764312709254128</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.216766156517068</v>
+        <v>-3.952385620855978</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-1.505104095031676</v>
+        <v>-1.254659018325782</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.5049529392925507</v>
+        <v>-0.253709513938162</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.559691481355522</v>
+        <v>-2.282468701692707</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.525755241611648</v>
+        <v>-2.224673895186633</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-2.020598113622512</v>
+        <v>-1.707117620943308</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.647204275344976</v>
+        <v>-3.28494676387573</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.1407</t>
+          <t>X ≈ -0.1406</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.6550341869380958</v>
+        <v>0.6491558867715597</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.2150132903916244</v>
+        <v>-0.5578793276971439</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-1.343599089866601</v>
+        <v>-1.32057721881025</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6240632731603952</v>
+        <v>0.289892467993397</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6483736937162874</v>
+        <v>-0.5685812512179069</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.35204539450352</v>
+        <v>-0.667528553884523</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-2.646361261479399</v>
+        <v>-2.954388578821522</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-1.641072161728907</v>
+        <v>-1.565954276167936</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.071132509586008</v>
+        <v>-2.345914010784256</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-2.92092104379109</v>
+        <v>-3.169731171200134</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.020129648499562</v>
+        <v>-2.260221756688708</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.56746062208525</v>
+        <v>-4.803046575965745</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-4.250912435932221</v>
+        <v>-4.456089434670574</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-4.026458067882899</v>
+        <v>-4.208373628128491</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.101</t>
+          <t>X ≈ -0.1008</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>205</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.224846259272681</v>
+        <v>-1.145995000938058</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-6.745180119335764</v>
+        <v>-6.409263789061086</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.083966766539497</v>
+        <v>-8.497521351593555</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.472757940704348</v>
+        <v>-7.603515184220143</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-9.011941817411468</v>
+        <v>-8.807448273405754</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-7.259235713637914</v>
+        <v>-6.803194612553021</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-10.2662954723216</v>
+        <v>-10.00347508427495</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-11.710799641648</v>
+        <v>-12.14860350065818</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-14.21079681525867</v>
+        <v>-14.13775711698235</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-17.01326864428508</v>
+        <v>-16.914153144933</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-20.14724755328692</v>
+        <v>-20.04752498616607</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-20.11932315198299</v>
+        <v>-19.99577375092989</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-19.08316333587015</v>
+        <v>-18.93455821134307</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-17.40059180922032</v>
+        <v>-17.22859304965376</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.06125</t>
+          <t>X ≈ -0.06106</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>3.180629511676656</v>
+        <v>2.217142953804739</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>7.077462450375684</v>
+        <v>6.665066981035693</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>8.534315828625672</v>
+        <v>7.263696594776476</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8.995424399072618</v>
+        <v>7.918860031634146</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>10.3217456962641</v>
+        <v>8.424056749495719</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>8.263279761896094</v>
+        <v>7.185430040891148</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>6.862085889693674</v>
+        <v>5.594657413417977</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>5.624840735675342</v>
+        <v>4.621210439836553</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5.861208173208539</v>
+        <v>4.359475780902336</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>5.829312501625026</v>
+        <v>3.80482799690234</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>4.851745427285437</v>
+        <v>2.866439275617765</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.117494211893124</v>
+        <v>1.687097711695074</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.466430540160545</v>
+        <v>0.5644960228949003</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>4.002825433508256</v>
+        <v>1.107422797814351</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.0215</t>
+          <t>X ≈ -0.02132</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.9957675156828643</v>
+        <v>-0.7859738938524998</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>1.353442430857271</v>
+        <v>1.571735720499035</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.948770056003212</v>
+        <v>1.670608569622644</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.09879717978949287</v>
+        <v>-0.1699507389164836</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>2.035755151446374</v>
+        <v>1.803854307323938</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>3.323228190982341</v>
+        <v>3.0618615010196</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>5.218715851518155</v>
+        <v>4.971648761547833</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>3.761548197830535</v>
+        <v>3.520594326287643</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>5.185714556159134</v>
+        <v>5.454065066904548</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>8.791241304383959</v>
+        <v>9.063734023035479</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>6.606342126321785</v>
+        <v>6.889150225745816</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>11.09616582323168</v>
+        <v>11.38081450005652</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>13.64631199962113</v>
+        <v>13.94132159812334</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>11.89184963004556</v>
+        <v>11.7273122729466</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ 0.01825</t>
+          <t>X ≈ 0.01842</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-3.862131500147484</v>
+        <v>-4.17677849155352</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-7.683262344592656</v>
+        <v>-7.982177798931723</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-4.763116602275872</v>
+        <v>-4.487026898357421</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.080405270842078</v>
+        <v>-3.801587301587055</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-2.961236260401989</v>
+        <v>-2.624169775872552</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-3.216348418612327</v>
+        <v>-2.906939812609316</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-1.091114026497159</v>
+        <v>-0.7453736796124275</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-1.558182670283898</v>
+        <v>-1.211206439995635</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.5907799245746688</v>
+        <v>0.4184876175342254</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.8116250596007504</v>
+        <v>-0.960896518836428</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>2.298590909211001</v>
+        <v>2.16829636696081</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.990427625102122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>4.675249147479441</v>
+        <v>4.609082955539527</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>7.6634157369325</v>
+        <v>7.635905595332673</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ 0.05801</t>
+          <t>X ≈ 0.05816</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.046054923822403</v>
+        <v>1.399353195689059</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.2647443494308632</v>
+        <v>0.2276987442781504</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.114786242684126</v>
+        <v>0.6570060234532491</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.074886904944599</v>
+        <v>2.432980599647173</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.536597351848904</v>
+        <v>1.120686191205628</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2407174151964213</v>
+        <v>-0.6641414586996248</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.74036553379878</v>
+        <v>-1.136320181669944</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-3.282122974265917</v>
+        <v>-3.659766110777561</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-4.172980649460996</v>
+        <v>-4.519783987404267</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-3.363148408446357</v>
+        <v>-3.697522033239544</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-4.397725085378745</v>
+        <v>-4.72470774826553</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-5.193222451695632</v>
+        <v>-5.078063644645489</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-5.198435545672844</v>
+        <v>-5.061698937464463</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-6.632450932790711</v>
+        <v>-6.458744610428518</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ 0.09774</t>
+          <t>X ≈ 0.09792</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.804798255179932</v>
+        <v>1.512876680860145</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.806387837883868</v>
+        <v>-1.794438335330163</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.9416979202182105</v>
+        <v>1.260099538424008</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.213791221907712</v>
+        <v>-1.483579638752055</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.6092236321462039</v>
+        <v>-0.2486908486694901</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.311849602511117</v>
+        <v>0.024094670149438</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7462971810798962</v>
+        <v>1.112863868280265</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.2922000341354831</v>
+        <v>0.07231846421876043</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>1.361103523627456</v>
+        <v>1.759483786116512</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.08261329872623</v>
+        <v>1.51036784897962</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.30648356903734</v>
+        <v>0.7315147577653747</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.055147435678407</v>
+        <v>2.226463104325703</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>3.349282296650642</v>
+        <v>3.555443108796354</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>4.432160804020064</v>
+        <v>4.666556936329002</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ 0.1375</t>
+          <t>X ≈ 0.1376</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.1908396946564892</v>
+        <v>-0.0386289351531417</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>3.923165051974287</v>
+        <v>3.701387896040806</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>6.581828781723075</v>
+        <v>6.349475002783144</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>5.185336368059566</v>
+        <v>4.9584464964693</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>5.792084982902757</v>
+        <v>5.609881766163767</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4.944420844598959</v>
+        <v>4.741982874336308</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>8.676504378462525</v>
+        <v>8.483608153932146</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>7.064397566736851</v>
+        <v>6.877090982902367</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>6.621736020901096</v>
+        <v>6.459890236883453</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>8.061893560449093</v>
+        <v>7.917430477361243</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>6.712154234250065</v>
+        <v>6.572605619178852</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>5.601494218666417</v>
+        <v>5.490087945897315</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>7.471419701230815</v>
+        <v>7.376298840626262</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>6.552117183518419</v>
+        <v>6.4846592919952</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ 0.1773</t>
+          <t>X ≈ 0.1774</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.4809160305343525</v>
+        <v>-0.2112612501743456</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.9492449807410352</v>
+        <v>-0.64501304797394</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-4.201159222638864</v>
+        <v>-3.912314254679373</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-6.356648364764858</v>
+        <v>-6.081280788177345</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-6.894937917860425</v>
+        <v>-6.570529929129201</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-4.88327817393975</v>
+        <v>-4.573606479275853</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-4.396559961777413</v>
+        <v>-4.05954992482328</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-1.435057176992657</v>
+        <v>-1.077106823137527</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-3.210325047801078</v>
+        <v>-2.838217363308743</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-2.345958129845293</v>
+        <v>-1.937908013089306</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.122087859534055</v>
+        <v>-2.716761104303565</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.373423992893017</v>
+        <v>-0.9344564359041883</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-2.936431989063507</v>
+        <v>-2.47903964982433</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-4.424982053122754</v>
+        <v>-3.954132718843454</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ 0.217</t>
+          <t>X ≈ 0.2171</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>183</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>2.710340800066682</v>
+        <v>2.68114500571405</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>3.831395144161377</v>
+        <v>3.830208357716721</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.075968021701421</v>
+        <v>5.075814631697099</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4.113296990426399</v>
+        <v>4.112802498048396</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.121455524762339</v>
+        <v>4.170001444528111</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.140141029807317</v>
+        <v>1.16409843875693</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-1.676809766617311</v>
+        <v>-1.62879808762699</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.690326497835812</v>
+        <v>-2.641078935442096</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.751308654358589</v>
+        <v>-2.678051544578892</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-3.054779363256685</v>
+        <v>-2.955432037962112</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>1.658552265368307</v>
+        <v>1.758460301386982</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.6000342428602963</v>
+        <v>0.7237308638885409</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.1798833895468874</v>
+        <v>0.328572937324715</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>2.591411389500195</v>
+        <v>2.763410149066857</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 0.2568</t>
+          <t>X ≈ 0.2569</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>211</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>4.86505553344675</v>
+        <v>4.835859739094118</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>6.571404985406559</v>
+        <v>6.570218198961904</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9.020235496386093</v>
+        <v>9.020082106381771</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9.150460639974476</v>
+        <v>9.149966147596473</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>9.560038385456984</v>
+        <v>9.608584305222756</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>11.27921336295934</v>
+        <v>11.30317077190895</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>11.66843665298235</v>
+        <v>11.71644833197267</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>13.57103625564111</v>
+        <v>13.62028381803483</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>12.56218680054009</v>
+        <v>12.63544391031979</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>10.29046705634296</v>
+        <v>10.38981438163754</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>10.08576589808277</v>
+        <v>10.18567393410144</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>10.59407769972716</v>
+        <v>10.7177743207554</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>11.12179414499195</v>
+        <v>11.27048369276978</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>14.19113169095308</v>
+        <v>14.36313045051974</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.2965</t>
+          <t>X ≈ 0.2966</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>183</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.57927668627206</v>
+        <v>-6.608472480624691</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-4.911774254745723</v>
+        <v>-4.912961041190378</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-6.399441814364117</v>
+        <v>-6.399595204368438</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-7.362112845639146</v>
+        <v>-7.362607338017149</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-9.539746661029987</v>
+        <v>-9.491200741264215</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-7.603028369099754</v>
+        <v>-7.57907096015014</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-8.780634903229341</v>
+        <v>-8.73262322423902</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-10.34059972187946</v>
+        <v>-10.29135215948575</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-9.308685703538856</v>
+        <v>-9.23542859375916</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-10.15860449986874</v>
+        <v>-10.05925717457417</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-8.177513308402098</v>
+        <v>-8.077605272383423</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-10.32892750577358</v>
+        <v>-10.20523088474534</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-10.20263027165529</v>
+        <v>-10.05394072387747</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-12.70913505858724</v>
+        <v>-12.53713629902057</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.3363</t>
+          <t>X ≈ 0.3364</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>135</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.593158043539724</v>
+        <v>1.563962249187092</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-4.46247249396859</v>
+        <v>-4.463659280413246</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-9.301688323168037</v>
+        <v>-9.301841713172358</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-6.208500216616713</v>
+        <v>-6.208994708994716</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-7.487530510453105</v>
+        <v>-7.438984590687333</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-10.89386018452176</v>
+        <v>-10.86990277557215</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-13.94153350675089</v>
+        <v>-13.89352182776057</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-12.18637992831541</v>
+        <v>-12.13713236592169</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-16.69180652928263</v>
+        <v>-16.61854941950293</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-16.06024384413101</v>
+        <v>-15.96089651883644</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-16.2649450023912</v>
+        <v>-16.16503696637253</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-14.0083446278137</v>
+        <v>-13.88464800678545</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-14.42849548112707</v>
+        <v>-14.27980593334924</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-14.94350057164127</v>
+        <v>-14.77150181207461</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>56</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-6.052344601962822</v>
+        <v>-6.081540396315454</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-9.449244980740936</v>
+        <v>-9.450431767185592</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-8.058302079781789</v>
+        <v>-8.058455469786111</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-9.713791221907819</v>
+        <v>-9.714285714285822</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-6.680652203574837</v>
+        <v>-6.632106283809065</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-11.74042103108271</v>
+        <v>-11.7164636221331</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-8.253702818920203</v>
+        <v>-8.205691139929883</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-3.363628605564081</v>
+        <v>-3.314381043170364</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-3.424610762086857</v>
+        <v>-3.351353652307161</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-4.274529558416717</v>
+        <v>-4.175182233122143</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-4.47923071667681</v>
+        <v>-4.379322680658134</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.659138278607209</v>
+        <v>-2.535441657578964</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.865003417634995</v>
+        <v>-4.716313869857167</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-8.210696338836939</v>
+        <v>-8.038697579270277</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>40</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.480916030534495</v>
+        <v>-2.510111824887126</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3.407897876401961</v>
+        <v>3.406711089957305</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-4.486873508353362</v>
+        <v>-4.487026898357684</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-16.85664836476486</v>
+        <v>-16.85714285714286</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-9.89493791786041</v>
+        <v>-9.846391998094639</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-9.597563888225181</v>
+        <v>-9.573606479275568</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-9.682274247491492</v>
+        <v>-9.634262568501171</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-10.14934289127837</v>
+        <v>-10.10009532888466</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-15.21032504780115</v>
+        <v>-15.13706793802145</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-13.56024384413101</v>
+        <v>-13.46089651883644</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-8.764945002391343</v>
+        <v>-8.665036966372668</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-6.106870229007633</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-9.150717703349287</v>
+        <v>-9.002028155571459</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-6.424982053123038</v>
+        <v>-6.252983293556376</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>40</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.01908396946564</v>
+        <v>4.989888175113009</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>3.407897876401684</v>
+        <v>3.406711089957028</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.5131264916469149</v>
+        <v>0.5129731016425936</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.6433516352351489</v>
+        <v>0.6428571428571459</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-2.394937917860695</v>
+        <v>-2.346391998094923</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4024361117745414</v>
+        <v>0.4263935207241545</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-2.182274247491776</v>
+        <v>-2.134262568501455</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>2.350657108721769</v>
+        <v>2.399904671115486</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>4.789674952198851</v>
+        <v>4.862932061978547</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.060243844131001</v>
+        <v>-0.960896518836428</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.264945002391194</v>
+        <v>-1.165036966372519</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-1.230566850035743</v>
+        <v>-1.106870229007498</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-4.150717703349137</v>
+        <v>-4.00202815557131</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-6.424982053122612</v>
+        <v>-6.25298329355595</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>61</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>9.814165936678762</v>
+        <v>9.784970142326131</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>18.03904541738542</v>
+        <v>18.03785863094077</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>16.0049297703353</v>
+        <v>16.00477638033098</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>16.13515491392366</v>
+        <v>16.13466042154566</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>17.2362096231231</v>
+        <v>17.28475554288887</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>17.533583652758</v>
+        <v>17.55754106170761</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>19.08821755578705</v>
+        <v>19.13622923477737</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>18.62114891200022</v>
+        <v>18.67039647439393</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>20.19951101777262</v>
+        <v>20.27276812755232</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>19.34959222144276</v>
+        <v>19.44893954673734</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>19.14489106318257</v>
+        <v>19.24479909920124</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>24.09730200242306</v>
+        <v>24.2209986234513</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>26.95583967369984</v>
+        <v>27.10452922147767</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>28.8209195862215</v>
+        <v>28.99291834578816</v>
       </c>
     </row>
     <row r="27">
@@ -1667,98 +1667,98 @@
         <v>51</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>8.303397694955841</v>
+        <v>8.274201900603209</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>8.652995915617502</v>
+        <v>8.651809129172847</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>14.14057747203893</v>
+        <v>14.14042408203461</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>18.19237124307828</v>
+        <v>18.19187675070027</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>19.61486600370802</v>
+        <v>19.6634119234738</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>19.91224003334322</v>
+        <v>19.93619744229284</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>15.90596104662602</v>
+        <v>15.95397272561634</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>19.36046103029026</v>
+        <v>19.40970859268398</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>17.33869456004199</v>
+        <v>17.41195166982168</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>14.52799144998664</v>
+        <v>14.62733877528122</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>16.28407460545193</v>
+        <v>16.38398264147061</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>22.20080569898368</v>
+        <v>22.32450232001192</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>17.85908621821923</v>
+        <v>18.00777576599706</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>16.12403755472038</v>
+        <v>16.29603631428704</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.5748</t>
+          <t>X ≈ 0.5747</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>40</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>20.01908396946565</v>
+        <v>19.98988817511302</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>18.40789787640182</v>
+        <v>18.40671108995716</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>20.51312649164678</v>
+        <v>20.51297310164246</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>15.64335163523514</v>
+        <v>15.64285714285714</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>12.60506208213945</v>
+        <v>12.65360800190522</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>15.40243611177453</v>
+        <v>15.42639352072415</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>15.31772575250837</v>
+        <v>15.36573743149869</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>17.35065710872163</v>
+        <v>17.39990467111534</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>14.78967495219885</v>
+        <v>14.86293206197855</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>11.43975615586899</v>
+        <v>11.53910348116356</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>8.735054997608799</v>
+        <v>8.834963033627474</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>6.269433149964186</v>
+        <v>6.393129770992431</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>3.349282296650856</v>
+        <v>3.497971844428683</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.075017946877317</v>
+        <v>1.247016706443979</v>
       </c>
     </row>
     <row r="29">
@@ -1771,150 +1771,150 @@
         <v>60</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>7.519083969465647</v>
+        <v>7.489888175113016</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>10.90789787640182</v>
+        <v>10.90671108995716</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>7.179793158313451</v>
+        <v>7.17963976830913</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8.97668496856847</v>
+        <v>8.976190476190467</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>6.771728748806119</v>
+        <v>6.820274668571891</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7.069102778441149</v>
+        <v>7.093060187390762</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>10.31772575250837</v>
+        <v>10.36573743149869</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>8.183990442054956</v>
+        <v>8.233238004448673</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>9.789674952198851</v>
+        <v>9.862932061978547</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>8.939756155868992</v>
+        <v>9.039103481163565</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>8.735054997608799</v>
+        <v>8.834963033627474</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.769433149964122</v>
+        <v>3.893129770992367</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>6.682615629983999</v>
+        <v>6.831305177761827</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.908351280210525</v>
+        <v>2.080350039777187</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.6543</t>
+          <t>X ≈ 0.6542</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>75</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-13.8142493638677</v>
+        <v>-13.84344515822033</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.425435456931517</v>
+        <v>-7.426622243376173</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-9.153540175019891</v>
+        <v>-9.153693565024213</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-5.023315031431544</v>
+        <v>-5.023809523809547</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.2282712511938882</v>
+        <v>-0.1797253314281164</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.597563888225444</v>
+        <v>-2.573606479275831</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-1.348940914158298</v>
+        <v>-1.300929235167978</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-3.149342891278373</v>
+        <v>-3.100095328884656</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.210325047801149</v>
+        <v>-3.137067938021453</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.060243844131008</v>
+        <v>-3.960896518836435</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.264945002391201</v>
+        <v>-4.165036966372526</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.897233516702542</v>
+        <v>-6.773536895674297</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.317384370015951</v>
+        <v>-7.168694822238123</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.758315386456083</v>
+        <v>-5.58631662688942</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.6941</t>
+          <t>X ≈ 0.694</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>37</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-3.832267381885629</v>
+        <v>-3.86146317623826</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-10.8488588803549</v>
+        <v>-10.85004566679956</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-27.45984648132619</v>
+        <v>-27.45999987133051</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-27.32962133773779</v>
+        <v>-27.33011583011579</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-25.16520818813078</v>
+        <v>-25.11666226836501</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-19.46242875309029</v>
+        <v>-19.43847134414068</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-22.24984181505916</v>
+        <v>-22.20183013606884</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-25.41961316154864</v>
+        <v>-25.37036559915493</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-22.77789261536871</v>
+        <v>-22.70463550558902</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-29.03321681710398</v>
+        <v>-28.93386949180941</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-21.12980986725603</v>
+        <v>-21.02990183123735</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-21.09543171490074</v>
+        <v>-20.9717350938725</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-18.81287986551145</v>
+        <v>-18.66419031773362</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-18.58714421528492</v>
+        <v>-18.41514545571825</v>
       </c>
     </row>
     <row r="32">
@@ -1927,150 +1927,150 @@
         <v>17</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>12.22496632240674</v>
+        <v>12.1957705280541</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>16.49613317051939</v>
+        <v>16.49494638407473</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>10.21900884458795</v>
+        <v>10.21885545458363</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>16.23158692935279</v>
+        <v>16.23109243697479</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>21.57565031743348</v>
+        <v>21.62419623719925</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>15.99067140589219</v>
+        <v>16.0146288148418</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>15.90596104662593</v>
+        <v>15.95397272561625</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>9.556539461662801</v>
+        <v>9.605787024056518</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>3.613204363963561</v>
+        <v>3.686461473743257</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>2.763285567633702</v>
+        <v>2.862632892928275</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>8.440937350549888</v>
+        <v>8.540845386568563</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>8.475315502905296</v>
+        <v>8.599012123933541</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>8.055164649591887</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>14.1632532409949</v>
+        <v>14.33525200056156</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.7735</t>
+          <t>X ≈ 0.7734</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>17</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.422092501122542</v>
+        <v>-5.451288295475173</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.61378022934299</v>
+        <v>10.61259344289834</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>16.10136178576443</v>
+        <v>16.10120839576011</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>22.11393987052926</v>
+        <v>22.11344537815125</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>21.57565031743352</v>
+        <v>21.62419623719929</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>21.87302434706865</v>
+        <v>21.89698175601826</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>27.67066692897892</v>
+        <v>27.71867860796924</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>27.20359828519221</v>
+        <v>27.25284584758592</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>33.02496906984591</v>
+        <v>33.09822617962561</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>32.17505027351601</v>
+        <v>32.27439759881058</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>26.08799617407938</v>
+        <v>26.18790421009805</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>14.35766844408173</v>
+        <v>14.48136506510998</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>8.055164649591887</v>
+        <v>8.203854197369715</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.398547358641956</v>
+        <v>2.570546118208618</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.8133</t>
+          <t>X ≈ 0.8132</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>12.03521300172368</v>
+        <v>10.82322150844634</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>13.64983336027278</v>
+        <v>12.57337775662382</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>13.25506197551774</v>
+        <v>12.17963976830912</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.15948066749321</v>
+        <v>8.976190476190467</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>16.07280401762335</v>
+        <v>15.15360800190525</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>22.82179095048421</v>
+        <v>22.09306018739082</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>16.28546768799227</v>
+        <v>15.36573743149872</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>19.0442054958184</v>
+        <v>18.2332380044487</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>18.98322333929562</v>
+        <v>18.1962653953119</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.90749809135289</v>
+        <v>14.03910348116359</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>17.92860338470557</v>
+        <v>17.1682963669608</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>14.73717508544802</v>
+        <v>13.8931297709924</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>11.09121778052167</v>
+        <v>10.1646385110952</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>4.865340527522406</v>
+        <v>3.747016706443915</v>
       </c>
     </row>
   </sheetData>
@@ -2210,885 +2210,885 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.3197</t>
+          <t>X &gt; -0.3194</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3900</v>
+        <v>3910</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.2918925562277224</v>
+        <v>0.2811193757247921</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2023764040091791</v>
+        <v>0.2157370970963797</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.2817278723678172</v>
+        <v>0.2949164834328144</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.4259603308873139</v>
+        <v>0.4387755102040813</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2598331233264517</v>
+        <v>0.2697090480904691</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.2898465518973623</v>
+        <v>0.3013297126588128</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.1935895866522088</v>
+        <v>0.2036235688486983</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-0.003413551800640846</v>
+        <v>0.007156969378875999</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.0009425578326585082</v>
+        <v>0.0098030709185295</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.04077663101625717</v>
+        <v>-0.0334565597153329</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-0.05177564548625213</v>
+        <v>-0.0699692433978214</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.07389240162994071</v>
+        <v>0.0536614683338783</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.2321328477914406</v>
+        <v>0.2098102489286688</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.139120510979815</v>
+        <v>0.1153031514566933</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.2799</t>
+          <t>X &gt; -0.2796</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3845</v>
+        <v>3855</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.3184618854843109</v>
+        <v>0.3078819703560427</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2506513117142362</v>
+        <v>0.2640940741826654</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.3886451638459576</v>
+        <v>0.4017470281815179</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.5331052020315141</v>
+        <v>0.519959342080945</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.3982639503283352</v>
+        <v>0.3813512731267465</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.5023582503678412</v>
+        <v>0.4872270697792942</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.3800310484585196</v>
+        <v>0.3631480995463292</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.05709699446558858</v>
+        <v>0.04105981227048261</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.0155198529959506</v>
+        <v>-0.03344099501627085</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.07167538479091462</v>
+        <v>-0.0915003021999965</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.1578763953225888</v>
+        <v>-0.1774786459992725</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.004936488715365783</v>
+        <v>-0.02701541957024034</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1875558275919573</v>
+        <v>0.1629096037646391</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.1159802355638462</v>
+        <v>0.08942915780577465</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.2401</t>
+          <t>X &gt; -0.2399</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3726</v>
+        <v>3735</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.3139489066146126</v>
+        <v>0.3180632017939189</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.2952708031005926</v>
+        <v>0.296889899671605</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.4502418248017221</v>
+        <v>0.4782694177129372</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5416385731366375</v>
+        <v>0.5427236315086787</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3393324971327516</v>
+        <v>0.3352319335291511</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.3569085274146033</v>
+        <v>0.3555946962517993</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1797670061917387</v>
+        <v>0.1759993235350379</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.03144364154632484</v>
+        <v>-0.03460481832597395</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.07765284195821209</v>
+        <v>-0.08359200219257445</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.2157398226832896</v>
+        <v>-0.2240684899517049</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-0.2445642032493467</v>
+        <v>-0.2527844249065012</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.1415110560444646</v>
+        <v>-0.1528964532516852</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.07050580080955626</v>
+        <v>0.05578769025294861</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.1447888164077824</v>
+        <v>-0.1619525037301202</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.2004</t>
+          <t>X &gt; -0.2001</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3607</v>
+        <v>3618</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.08814474294630514</v>
+        <v>0.09247699362031625</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.0440225436037025</v>
+        <v>-0.04370213318333072</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1289363313372149</v>
+        <v>0.1285696847231961</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1913195644582615</v>
+        <v>0.1908174515671703</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.0829381883341398</v>
+        <v>0.07503066526336255</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.06357027498338397</v>
+        <v>0.05959815392878198</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-0.172036284016265</v>
+        <v>-0.1790901547082058</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.4579506964264439</v>
+        <v>-0.4643337394806792</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.4761057786981553</v>
+        <v>-0.4862260942455734</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7293105846461003</v>
+        <v>-0.7427849782511231</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-0.8078812904798411</v>
+        <v>-0.82120929445869</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.647302787968826</v>
+        <v>-0.6648812787313858</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-0.3591434239701314</v>
+        <v>-0.3815528861600157</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.4782118840071448</v>
+        <v>-0.5039506788518366</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.1606</t>
+          <t>X &gt; -0.1604</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3391</v>
+        <v>3399</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.5155587050708164</v>
+        <v>0.5086455021939074</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.4480095425787241</v>
+        <v>0.4361745903969165</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.568975991940718</v>
+        <v>0.5569613714371755</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3625518704600736</v>
+        <v>0.3509826928718027</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.3991797291982735</v>
+        <v>0.3766126967408923</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.4186173415479999</v>
+        <v>0.4014448855612471</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.2029523563930056</v>
+        <v>0.1807697274470144</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.218521578355201</v>
+        <v>-0.239596063099043</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.4105606190614566</v>
+        <v>-0.4367154115819787</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.7436017233651739</v>
+        <v>-0.774296460064761</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-0.6962944425797701</v>
+        <v>-0.7270593061726487</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.5276490781525922</v>
+        <v>-0.5643827253322442</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.2533120429719347</v>
+        <v>-0.296145802630285</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2763533300322223</v>
+        <v>-0.3247691129147228</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.1209</t>
+          <t>X &gt; -0.1207</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3120</v>
+        <v>3130</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.5034440077675981</v>
+        <v>0.4965696895896343</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.5055990258271095</v>
+        <v>0.5216060613129869</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.735100301931034</v>
+        <v>0.7183217167331932</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3398372582383402</v>
+        <v>0.356232939035479</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.4901691450988608</v>
+        <v>0.4578450200638713</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.4855563163781085</v>
+        <v>0.4933151268426954</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.4504408148684576</v>
+        <v>0.4502130451422985</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.09496029370959747</v>
+        <v>-0.12560553296629</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.2663250478011463</v>
+        <v>-0.2726341262192165</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.5544820003409967</v>
+        <v>-0.5684268315358665</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.5813074743732756</v>
+        <v>-0.5952955045148798</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.1767551908430605</v>
+        <v>-0.2001013912043135</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.09391542705763101</v>
+        <v>0.06137011973994788</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.04937692123621673</v>
+        <v>0.008997537114829868</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.08113</t>
+          <t>X &gt; -0.08093</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2915</v>
+        <v>2925</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.6953134776623742</v>
+        <v>0.6116896080710532</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>1.015516598643025</v>
+        <v>1.007359332877662</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.425635035734274</v>
+        <v>1.3642184104108</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.9595909514744534</v>
+        <v>0.9140956280157866</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.158413655326861</v>
+        <v>1.107207456016447</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.030215790187128</v>
+        <v>1.004694441911454</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.204104944842378</v>
+        <v>1.182864691819397</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.7219340686668545</v>
+        <v>0.717031931436054</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.7143324864454286</v>
+        <v>0.6991095363812718</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.6029969917716969</v>
+        <v>0.5771710810270037</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.7946848810906317</v>
+        <v>0.7680231429170874</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.225723859597309</v>
+        <v>1.187287611784996</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>1.44256076029955</v>
+        <v>1.392708686533808</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>1.276561686156839</v>
+        <v>1.21710217652938</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.04138</t>
+          <t>X &gt; -0.04119</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>2728</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.5249490721049384</v>
+        <v>0.495753277752307</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.5999799878387648</v>
+        <v>0.5987932013941091</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.9383464329957505</v>
+        <v>0.9381930429914291</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.4087475296632874</v>
+        <v>0.4082530372852844</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.530282023488418</v>
+        <v>0.5788279432541898</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.5344009211586922</v>
+        <v>0.5583583301083053</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.8162594768485363</v>
+        <v>0.8642711558388569</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3858477245574008</v>
+        <v>0.4350952869511175</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.3615224595302209</v>
+        <v>0.4347795693099172</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2447414931124001</v>
+        <v>0.3440888184069735</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.5165799242950229</v>
+        <v>0.6164879603136981</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>1.027497666093161</v>
+        <v>1.151194287121406</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.303827751196174</v>
+        <v>1.452517298974001</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>1.089680703475487</v>
+        <v>1.225022571546553</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.001627</t>
+          <t>X &gt; -0.001449</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2526</v>
+        <v>2525</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.6465582370824308</v>
+        <v>0.5987990662021261</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.5397268550241492</v>
+        <v>0.5205724760957793</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.8575445439033089</v>
+        <v>0.8793097353058315</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.4335337413317362</v>
+        <v>0.4547383309759567</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4098918525274087</v>
+        <v>0.480340675172549</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.311383063476832</v>
+        <v>0.3570865900310807</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4642023954220633</v>
+        <v>0.5340542631818579</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.1158985972410278</v>
+        <v>0.1870333839866376</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.02426012301888392</v>
+        <v>0.03124889366171857</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.438707818794505</v>
+        <v>-0.3569361227968244</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.02959181471093331</v>
+        <v>0.1121907563997482</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.2223230945405206</v>
+        <v>0.3287733353487994</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.3168199055184928</v>
+        <v>0.4484668939334853</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.225849300796483</v>
+        <v>0.3806800727805353</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; 0.03813</t>
+          <t>X &gt; 0.03829</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>2345</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.9945637136021048</v>
+        <v>0.9653679192494735</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.174422396657683</v>
+        <v>1.173235610213027</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.291378090793899</v>
+        <v>1.291224700789577</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.7819443857681847</v>
+        <v>0.7814498933901817</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.6700940650818765</v>
+        <v>0.7186399848476483</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.5836727855485293</v>
+        <v>0.6076301944981424</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.5842502727642298</v>
+        <v>0.6322619517545505</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2451133987003047</v>
+        <v>0.2943609610940214</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.07173229726810604</v>
+        <v>0.001524812511590312</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.4099240147066965</v>
+        <v>-0.3105766894121231</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.145542017316572</v>
+        <v>-0.04563398129789675</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.06851994172031084</v>
+        <v>0.0551766793079338</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.01958763938340269</v>
+        <v>0.1291019083944249</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.3482229912890631</v>
+        <v>-0.1762242317224008</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; 0.07788</t>
+          <t>X &gt; 0.07803</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2104</v>
+        <v>2102</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.9886657185150796</v>
+        <v>0.9151974044184428</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>1.278620309861893</v>
+        <v>1.282543630394841</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.31160557909925</v>
+        <v>1.364543035039219</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.6338459318130916</v>
+        <v>0.5905260296316399</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.5708415498200594</v>
+        <v>0.6721617602306225</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.6781015110140842</v>
+        <v>0.7546523218659189</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7359767030787125</v>
+        <v>0.8367174505281767</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.6491361961740978</v>
+        <v>0.7514746045121043</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.3980399712102596</v>
+        <v>0.5242070381916761</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.07165068823746878</v>
+        <v>0.08096837174395688</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.3415188759357974</v>
+        <v>0.4952865350546887</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.5184825796219172</v>
+        <v>0.6486007510113936</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.5736168974111635</v>
+        <v>0.7291802174066575</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.3715958936452992</v>
+        <v>0.5500614257588481</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; 0.1176</t>
+          <t>X &gt; 0.1178</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>1754</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.8258114495112565</v>
+        <v>0.7966156551586252</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.894214866139556</v>
+        <v>1.893028079694901</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.385418395865706</v>
+        <v>1.385265005861385</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.002530654619406</v>
+        <v>1.002036162241403</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.8063163580801529</v>
+        <v>0.8548622778459247</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.8756402166776098</v>
+        <v>0.8995976256272229</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.7339173146520324</v>
+        <v>0.781928993642353</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.8369740984593648</v>
+        <v>0.8862216608530815</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.2058665143425173</v>
+        <v>0.2791236241222137</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.3019770254309009</v>
+        <v>-0.2026297001363275</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.3485099577000241</v>
+        <v>0.4484179937186994</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.2118504817771196</v>
+        <v>0.3355471028053643</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.0197497995013407</v>
+        <v>0.1684393472791683</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.4386650633850167</v>
+        <v>-0.2666663038183543</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; 0.1574</t>
+          <t>X &gt; 0.1575</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.9373145324683279</v>
+        <v>0.9439458545228092</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>1.537924686053294</v>
+        <v>1.574048447435359</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.4729120144349892</v>
+        <v>0.5096196475847776</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2680165145917073</v>
+        <v>0.3041582830315193</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.06920065244499796</v>
+        <v>0.01611638554036432</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.1611492485037544</v>
+        <v>0.2218328232057019</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.6608265263120074</v>
+        <v>-0.5765831587092336</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2565814971764979</v>
+        <v>-0.1705178640959204</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.9207808118762131</v>
+        <v>-0.8111122036150107</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.770699608206073</v>
+        <v>-1.634940784429993</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.7689664501123801</v>
+        <v>-0.6318377712015035</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.7345882977570568</v>
+        <v>-0.5736710338366109</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.288787408443113</v>
+        <v>-1.102967122707611</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.666268916393534</v>
+        <v>-1.457543991074537</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; 0.1971</t>
+          <t>X &gt; 0.1972</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>1317</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.125765822161163</v>
+        <v>1.096570027808532</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.868414201382834</v>
+        <v>1.867227414938178</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.093992095291426</v>
+        <v>1.093838705287105</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.148287094612513</v>
+        <v>1.14779260223451</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.8377879743186369</v>
+        <v>0.8863338940844088</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.8314414268846377</v>
+        <v>0.8553988358342508</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1644306635888171</v>
+        <v>-0.1164189845984964</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.09998829750464466</v>
+        <v>-0.05074073511092791</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.6165513196310712</v>
+        <v>-0.5432942098513749</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.694260548762749</v>
+        <v>-1.594913223468176</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4562889659447293</v>
+        <v>-0.3563809299260541</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.6497012463912313</v>
+        <v>-0.5260046253629866</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.06985209970464</v>
+        <v>-0.9211625519268125</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.299697315081751</v>
+        <v>-1.127698555515089</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; 0.2369</t>
+          <t>X &gt; 0.237</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>1134</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8700539871023381</v>
+        <v>0.8408581927497067</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.551636853474129</v>
+        <v>1.550450067029473</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4513980965850521</v>
+        <v>0.4512447065807308</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.669806661690167</v>
+        <v>0.669312169312164</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.3078839516279857</v>
+        <v>0.3564298713937575</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.7816248242965784</v>
+        <v>0.8055822332461915</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.0796305144131324</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3180292427604314</v>
+        <v>0.3672768051541482</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2720534428628767</v>
+        <v>-0.1987963330831803</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-1.474705925259755</v>
+        <v>-1.375358599965182</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.7975728683523968</v>
+        <v>-0.6976648323337216</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.8513781375138336</v>
+        <v>-0.727681516485589</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.271528990827242</v>
+        <v>-1.122839443049415</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.927627555768254</v>
+        <v>-1.755628796201592</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.2766</t>
+          <t>X &gt; 0.2767</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>923</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.04321288860585781</v>
+        <v>-0.07240868295848912</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4041058937365989</v>
+        <v>0.4029191072919431</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-1.507458557107277</v>
+        <v>-1.507611947111599</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-1.26889105165543</v>
+        <v>-1.269385544033433</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-1.807180604751125</v>
+        <v>-1.758634684985353</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-1.618148936979523</v>
+        <v>-1.59419152802991</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-2.569598191153609</v>
+        <v>-2.521586512163289</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-2.711639749349878</v>
+        <v>-2.662392186956161</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.20599135332661</v>
+        <v>-3.132734243546913</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-4.164252511519962</v>
+        <v>-4.064905186225388</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-3.285530051145258</v>
+        <v>-3.185622015126583</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-3.46783662251692</v>
+        <v>-3.344140001488675</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-4.104672199557307</v>
+        <v>-3.955982651779479</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-5.612414339146589</v>
+        <v>-5.440415579579927</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.3164</t>
+          <t>X &gt; 0.3165</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>740</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>1.573138023519704</v>
+        <v>1.543942229167072</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>1.718708687212626</v>
+        <v>1.71752190076797</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.297684319164027</v>
+        <v>-0.2978377091683484</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.2379462298297312</v>
+        <v>0.2374517374517282</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1050620821394546</v>
+        <v>0.1536080019052264</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.138104428766006</v>
+        <v>-0.114147019816393</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.033625598842988</v>
+        <v>-0.9856139198526677</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.82501856695405</v>
+        <v>-0.7757710045603332</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.69681153428764</v>
+        <v>-1.623554424507944</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.68186546575263</v>
+        <v>-2.582518140458056</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.075755813202008</v>
+        <v>-1.975847777183333</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.771107390576418</v>
+        <v>-1.647410769548173</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.59666364929523</v>
+        <v>-2.447974101517403</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-3.857414485555189</v>
+        <v>-3.685415725988527</v>
       </c>
     </row>
     <row r="23">
@@ -3101,46 +3101,46 @@
         <v>605</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.568670746325154</v>
+        <v>1.539474951972522</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>3.097980521029925</v>
+        <v>3.096793734585269</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.711473599084798</v>
+        <v>1.711320209080476</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1.676409486474803</v>
+        <v>1.6759149940968</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.799276958172506</v>
+        <v>1.847822877938277</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>2.261940244005942</v>
+        <v>2.285897652955555</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.846651372343082</v>
+        <v>1.894663051333403</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.710161240953035</v>
+        <v>1.759408803346751</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>1.649179084430259</v>
+        <v>1.722436194209955</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3033925195053513</v>
+        <v>0.4027398447999246</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.090426898435247</v>
+        <v>1.190334934453922</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.9595157945922281</v>
+        <v>1.083212415620473</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.04349717268377162</v>
+        <v>0.1921867204615992</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.383659739073167</v>
+        <v>-1.211660979506505</v>
       </c>
     </row>
     <row r="24">
@@ -3153,46 +3153,46 @@
         <v>549</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>2.346042075112273</v>
+        <v>2.316846280759641</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>4.377843231593076</v>
+        <v>4.37665644514842</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>2.70802630949742</v>
+        <v>2.707872919493099</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2.838251453085782</v>
+        <v>2.837756960707779</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.664260624944546</v>
+        <v>2.712806544710318</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.690232104488565</v>
+        <v>3.714189513438178</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.876924295313465</v>
+        <v>2.924935974303786</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.227706289049493</v>
+        <v>2.27695385144321</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.166724132526717</v>
+        <v>2.239981242306413</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.7703572487651655</v>
+        <v>0.8697045740597389</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>1.658552265368357</v>
+        <v>1.758460301387032</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.328631692769221</v>
+        <v>1.452328313797466</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.5441821145013535</v>
+        <v>0.6928716622791811</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.6872771350899711</v>
+        <v>-0.5152783755233088</v>
       </c>
     </row>
     <row r="25">
@@ -3205,46 +3205,46 @@
         <v>509</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.725370806400818</v>
+        <v>2.696175012048187</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>4.454066835144445</v>
+        <v>4.452880048699789</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.273440833493545</v>
+        <v>3.273287443489224</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4.385984248201744</v>
+        <v>4.385489755823741</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.651231040882074</v>
+        <v>3.699776960647846</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4.734459687413036</v>
+        <v>4.758417096362649</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>3.863894711250992</v>
+        <v>3.911906390241313</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>3.200362413240292</v>
+        <v>3.249609975634009</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>3.532307565165453</v>
+        <v>3.60556467494515</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>1.896534151939719</v>
+        <v>1.995881477234292</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>2.477687610575401</v>
+        <v>2.577595646594077</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.922674800258818</v>
+        <v>2.046371421287063</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>1.30606029272144</v>
+        <v>1.454749840499268</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.2363769450677395</v>
+        <v>-0.06437818550107721</v>
       </c>
     </row>
     <row r="26">
@@ -3257,46 +3257,46 @@
         <v>469</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.529744950275884</v>
+        <v>2.500549155923252</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>4.543292332691799</v>
+        <v>4.542105546247143</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>3.508862099322684</v>
+        <v>3.508708709318363</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4.705185323934501</v>
+        <v>4.704690831556498</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>4.166895770838806</v>
+        <v>4.215441690604578</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5.103928649087962</v>
+        <v>5.127886058037575</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4.379559441207725</v>
+        <v>4.427571120198046</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>3.27283194880691</v>
+        <v>3.322079511200627</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>3.425069408488831</v>
+        <v>3.498326518268527</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.148711379749592</v>
+        <v>2.248058705044166</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>2.796888686308158</v>
+        <v>2.896796722326833</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>2.191607990049405</v>
+        <v>2.31530461107765</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>1.771457136735997</v>
+        <v>1.920146684513824</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.2914358573250055</v>
+        <v>0.4634346168916679</v>
       </c>
     </row>
     <row r="27">
@@ -3309,46 +3309,46 @@
         <v>408</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.440652596916628</v>
+        <v>1.411456802563997</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.525544935225348</v>
+        <v>2.524358148780692</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.640577472038935</v>
+        <v>1.640424082034613</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2.996292811705729</v>
+        <v>2.995798319327726</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>2.212905219394344</v>
+        <v>2.261451139160116</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>3.245573366676503</v>
+        <v>3.269530775626116</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>2.180470850547579</v>
+        <v>2.228482529537899</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.9781080891137819</v>
+        <v>1.027355651507499</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.9171259325910057</v>
+        <v>0.9903830423707021</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.4229889421702211</v>
+        <v>-0.3236416168756477</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.352702056432328</v>
+        <v>0.4526100924510033</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.083508026506465</v>
+        <v>-0.9598114054782201</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-1.993854958251255</v>
+        <v>-1.845165410473427</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-3.974001660965889</v>
+        <v>-3.802002901399227</v>
       </c>
     </row>
     <row r="28">
@@ -3361,98 +3361,98 @@
         <v>357</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.4602604400538866</v>
+        <v>0.4310646457012552</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.650194795169327</v>
+        <v>1.649008008724671</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1451368136753501</v>
+        <v>-0.1452902036796715</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.8254244643667974</v>
+        <v>0.8249299719887944</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2730891783647564</v>
+        <v>-0.2245432585989846</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.8646209857241161</v>
+        <v>0.8885783946737291</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.2196865368220955</v>
+        <v>0.2676982158124162</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-1.647942331054281</v>
+        <v>-1.598694768660565</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.428812442759131</v>
+        <v>-1.355555332979435</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.558843283906917</v>
+        <v>-2.459495958612344</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.923208307713331</v>
+        <v>-1.823300271694656</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-4.409838558719343</v>
+        <v>-4.286141937691099</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-4.829989412032752</v>
+        <v>-4.681299864254925</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-6.845150120349643</v>
+        <v>-6.673151360782981</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.5947</t>
+          <t>X &gt; 0.5946</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>317</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-2.007729910660537</v>
+        <v>-2.036925705013168</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.46434187123225</v>
+        <v>-0.4655286576769058</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-2.75185773548256</v>
+        <v>-2.752011125486881</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-1.04434552564814</v>
+        <v>-1.044840018026143</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-1.89809249199304</v>
+        <v>-1.849546572227268</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.9698036358595346</v>
+        <v>-0.9458462269099215</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.685428821624122</v>
+        <v>-1.637417142633801</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-4.045241944906131</v>
+        <v>-3.995994382512414</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-3.475309274930488</v>
+        <v>-3.402052165150792</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-4.325228071260348</v>
+        <v>-4.225880745965775</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-3.268099576523689</v>
+        <v>-3.168191540505013</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-5.757380730162062</v>
+        <v>-5.633684109133817</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-5.862074170226265</v>
+        <v>-5.713384622448437</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-7.844540412744209</v>
+        <v>-7.672541653177547</v>
       </c>
     </row>
     <row r="30">
@@ -3465,98 +3465,98 @@
         <v>257</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-4.231888793180268</v>
+        <v>-4.261084587532899</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-3.119339477683788</v>
+        <v>-3.120526264128443</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-5.070531095901856</v>
+        <v>-5.070684485906177</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-3.383885718850465</v>
+        <v>-3.384380211228468</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-3.922175271946159</v>
+        <v>-3.873629352180387</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-2.846591125579543</v>
+        <v>-2.82263371662993</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-4.487721718308755</v>
+        <v>-4.439710039318435</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-6.900315653924288</v>
+        <v>-6.851068091530571</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-6.572192752081307</v>
+        <v>-6.49893564230161</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-7.422111548411166</v>
+        <v>-7.322764223116593</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-6.070392473208322</v>
+        <v>-5.970484437189647</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-7.981539612681793</v>
+        <v>-7.857842991653548</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-8.790795524360959</v>
+        <v>-8.642105976583132</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-10.12148010759746</v>
+        <v>-9.949481348030801</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.6742</t>
+          <t>X &gt; 0.6741</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>182</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.2831138327321483</v>
+        <v>-0.3123096270847796</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.344849376345429</v>
+        <v>-1.346036162790085</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-3.387972409452125</v>
+        <v>-3.388125799456446</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.708296716413201</v>
+        <v>-2.708791208791204</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-5.4443884673111</v>
+        <v>-5.395842547545328</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-2.949212239873809</v>
+        <v>-2.925254830924196</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-5.781175346392736</v>
+        <v>-5.733163667402415</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-8.446046187981672</v>
+        <v>-8.396798625587955</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-7.957577795053901</v>
+        <v>-7.884320685274204</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-8.80749659138376</v>
+        <v>-8.708149266089187</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-6.814395551841748</v>
+        <v>-6.714487515823073</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-8.428369047838075</v>
+        <v>-8.30467242680983</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-9.397970450602038</v>
+        <v>-9.249280902824211</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-11.91948754762825</v>
+        <v>-11.74748878806159</v>
       </c>
     </row>
     <row r="32">
@@ -3569,202 +3569,202 @@
         <v>145</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.6225322453277116</v>
+        <v>0.5933364509750803</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.080311669505264</v>
+        <v>1.079124883060608</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.754505801991613</v>
+        <v>2.754352411987291</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3.574386117993768</v>
+        <v>3.573891625615765</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.4121792971709013</v>
+        <v>-0.3636333774051295</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.264505077291773</v>
+        <v>1.288462486241386</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-1.57882597162957</v>
+        <v>-1.530814292639249</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-4.114860132657682</v>
+        <v>-4.065612570263966</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-4.175842289180459</v>
+        <v>-4.102585179400762</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-3.646450740682731</v>
+        <v>-3.547103415388158</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-3.161496726529137</v>
+        <v>-3.061588690510462</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-5.196084091415187</v>
+        <v>-5.072387470386943</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-6.995545289556183</v>
+        <v>-6.846855741778356</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-10.21808550139862</v>
+        <v>-10.04608674183196</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.7537</t>
+          <t>X &gt; 0.7536</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>128</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.9184160305343525</v>
+        <v>-0.9476118248869838</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.9671021235981812</v>
+        <v>-0.9682889100428369</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.76312649164678</v>
+        <v>1.762973101642459</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.893351635235142</v>
+        <v>1.892857142857139</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-3.332437917860553</v>
+        <v>-3.283891998094781</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.6913138882254657</v>
+        <v>-0.6673564792758526</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-3.901024247491634</v>
+        <v>-3.853012568501313</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-5.930592891278373</v>
+        <v>-5.881345328884656</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-4.497743844131008</v>
+        <v>-4.398396518836435</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-4.702445002391201</v>
+        <v>-4.602536966372526</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-7.011816850035878</v>
+        <v>-6.888120229007633</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-8.994467703349287</v>
+        <v>-8.845778155571459</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-13.45623205312275</v>
+        <v>-13.28423329355609</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.7934</t>
+          <t>X &gt; 0.7933</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>111</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.2286637782821046</v>
+        <v>-0.2578595726347359</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.740750772246834</v>
+        <v>-2.74193755869149</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.4328194542991639</v>
+        <v>-0.4329728443034853</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-1.203495211611703</v>
+        <v>-1.203989703989706</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-7.1471901701128</v>
+        <v>-7.098644250347029</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-4.147113437775019</v>
+        <v>-4.123156028825406</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-8.736328301545683</v>
+        <v>-8.688316622555362</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-11.00519874713423</v>
+        <v>-10.95595118474051</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-11.06618090365701</v>
+        <v>-10.99292379387731</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-10.11429789818506</v>
+        <v>-10.01495057289048</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-9.418098155544357</v>
+        <v>-9.318190119525681</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-10.28462090408993</v>
+        <v>-10.16092428306168</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-11.60567265830424</v>
+        <v>-11.45698311052642</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-15.88444151258221</v>
+        <v>-15.71244275301555</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.8332</t>
+          <t>X &gt; 0.8331</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-4.980916030534353</v>
+        <v>-4.361963676738839</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-9.092102123598181</v>
+        <v>-8.414276564363824</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-5.73687350835322</v>
+        <v>-5.104310848974826</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-5.606648364764858</v>
+        <v>-4.974426807760146</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-16.14493791786055</v>
+        <v>-15.34021915858861</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-14.59756388822547</v>
+        <v>-13.83286573853511</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-18.43227424749163</v>
+        <v>-17.59722553146428</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-22.64934289127837</v>
+        <v>-21.76676199555133</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-22.71032504780115</v>
+        <v>-21.80373460468812</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-19.81024384413101</v>
+        <v>-18.9238594817994</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-20.0149450023912</v>
+        <v>-19.12799992933549</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-19.98056685003588</v>
+        <v>-19.0698331919706</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-20.40071770334929</v>
+        <v>-19.46499111853442</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-23.92498205312275</v>
+        <v>-22.91964996022276</v>
       </c>
     </row>
   </sheetData>
@@ -3904,885 +3904,885 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.3197</t>
+          <t>X &lt; -0.3194</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-8.730916030534353</v>
+        <v>-8.065667380442541</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.592102123598181</v>
+        <v>-7.179708663129261</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.98687350835322</v>
+        <v>-7.573446651443966</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.106648364764858</v>
+        <v>-8.678130511463849</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-7.394937917860553</v>
+        <v>-7.932811751181205</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-9.597563888225466</v>
+        <v>-10.12916203483141</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.18227424749163</v>
+        <v>-12.65895392652601</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-11.39934289127837</v>
+        <v>-11.89021878567478</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-5.210325047801149</v>
+        <v>-5.754351888638737</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-4.810243844131016</v>
+        <v>-5.34361256821915</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-3.764945002391201</v>
+        <v>-3.078617213286101</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-4.980566850035885</v>
+        <v>-4.255018377155785</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-7.900717703349287</v>
+        <v>-7.119312106188744</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-5.174982053122761</v>
+        <v>-4.401131441704244</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.2799</t>
+          <t>X &lt; -0.2796</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-5.814249363867688</v>
+        <v>-5.451288295475223</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-5.203213234709295</v>
+        <v>-5.563877145336953</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.079466100945808</v>
+        <v>-7.42820336894578</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.689981698098194</v>
+        <v>-7.2983193277311</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-8.228271251193888</v>
+        <v>-7.78756846868302</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-11.6346009252625</v>
+        <v>-11.19125353809938</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-12.46005202526941</v>
+        <v>-11.9872037449719</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-8.482676224611708</v>
+        <v>-8.041271799472895</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-2.617732455208561</v>
+        <v>-2.195891467433214</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.986169770056932</v>
+        <v>-1.549131812954087</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.7720920346458371</v>
+        <v>1.187904210098061</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.6750112944803206</v>
+        <v>-0.2245172878311621</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-3.317384370015951</v>
+        <v>-2.825557567336169</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-2.350907979048678</v>
+        <v>-1.841218587673744</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.2401</t>
+          <t>X &lt; -0.2399</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-2.874616817935923</v>
+        <v>-2.900736824886984</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-3.304700548795033</v>
+        <v>-3.312038910042837</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-4.877651898357541</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-3.962947577363288</v>
+        <v>-3.966517857142861</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.320134768254256</v>
+        <v>-3.283891998094781</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.810162313422317</v>
+        <v>-3.792356479275853</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-3.501171885286908</v>
+        <v>-3.462387568501313</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-3.180838954270506</v>
+        <v>-3.146970328884656</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.4859155989822455</v>
+        <v>-0.4495679380214526</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1.02637032909734</v>
+        <v>1.070353481163565</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>1.609070745640295</v>
+        <v>1.647463033627474</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.643448897995619</v>
+        <v>1.705629770992367</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.04219568247748384</v>
+        <v>0.138596844428541</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>2.630136057113461</v>
+        <v>2.731391706443908</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.2004</t>
+          <t>X &lt; -0.2001</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>373</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.3340973742913889</v>
+        <v>0.3049015799387575</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>1.135779913935338</v>
+        <v>1.134593127490682</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.2048154996896798</v>
+        <v>0.2046621096853585</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.8712336727686605</v>
+        <v>0.8707391803906575</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.3329441196729661</v>
+        <v>0.3814900394387379</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.3622216345627436</v>
+        <v>0.3861790435123567</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>1.081800819532496</v>
+        <v>1.129812498522817</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>1.955214749472304</v>
+        <v>2.004462311866021</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>3.502811681421363</v>
+        <v>3.57606879120106</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>5.6019545472899</v>
+        <v>5.701301872584473</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.469639448010938</v>
+        <v>6.569547484029613</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>5.967824570875649</v>
+        <v>6.091521191903894</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>4.207191143835693</v>
+        <v>4.355880691613521</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>4.969119823552845</v>
+        <v>5.141118583119507</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.1606</t>
+          <t>X &lt; -0.1604</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-2.226247100143866</v>
+        <v>-2.172273987049145</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-2.139640323937741</v>
+        <v>-2.066261883015805</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.364632421765783</v>
+        <v>-2.291080952411598</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3668351219804791</v>
+        <v>-0.303088803088805</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-1.584241822784151</v>
+        <v>-1.468013619716402</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-1.796205653930052</v>
+        <v>-1.701984857654232</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-1.541357439342228</v>
+        <v>-1.424803109041854</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.3106332138590204</v>
+        <v>-0.2014466802360033</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>1.665736072742149</v>
+        <v>1.788607737654225</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.362506580317202</v>
+        <v>3.498562940623025</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.15780542205701</v>
+        <v>3.294422493086934</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>2.852625000558355</v>
+        <v>3.014751392613988</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.923136286463951</v>
+        <v>2.112836709293411</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>1.809313362836505</v>
+        <v>2.02404373347094</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.1209</t>
+          <t>X &lt; -0.1207</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-1.318125332859928</v>
+        <v>-1.290599629765033</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-1.533962588714459</v>
+        <v>-1.596192510507414</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-2.045013043236942</v>
+        <v>-1.989930498822119</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-0.05432278336950702</v>
+        <v>-0.1178861788617951</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1.290286755069857</v>
+        <v>-1.187855412728922</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1.341749934737095</v>
+        <v>-1.379645968242173</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-1.891576573073024</v>
+        <v>-1.904878131799805</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.7307382401155778</v>
+        <v>-0.6285506134375041</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.4873493708034999</v>
+        <v>0.4959169632561284</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1.38161662098527</v>
+        <v>1.414248661186789</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.525752672027402</v>
+        <v>1.558540269399835</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.5136191964757444</v>
+        <v>0.5714108395173412</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.02281072660509409</v>
+        <v>0.0601088943704724</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.02963321591344936</v>
+        <v>0.07686571921975371</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.08113</t>
+          <t>X &lt; -0.08093</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.495000537576608</v>
+        <v>-1.251957118456417</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.542806348950293</v>
+        <v>-2.507468014520455</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.407061301780445</v>
+        <v>-3.226522696676874</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.68059202673669</v>
+        <v>-1.553404539385852</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-2.782261861522528</v>
+        <v>-2.648075814745859</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-2.484887831887441</v>
+        <v>-2.420048426841397</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-3.508565327303849</v>
+        <v>-3.462753665033645</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.848873407710293</v>
+        <v>-2.84868819942875</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-2.346475282542926</v>
+        <v>-2.322809026201561</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-2.163530229107536</v>
+        <v>-2.114742672682588</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.649921528212801</v>
+        <v>-2.600309011400668</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.460613798392686</v>
+        <v>-3.386419947581743</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-3.692971224476054</v>
+        <v>-3.593960613357574</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-3.37333886063449</v>
+        <v>-3.251107120948213</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.04138</t>
+          <t>X &lt; -0.04119</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1252</v>
+        <v>1263</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.781311287451345</v>
+        <v>-0.707603987896384</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-1.085773009674128</v>
+        <v>-1.073681066905586</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.596928931947843</v>
+        <v>-1.58278827983321</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-0.07772601928149925</v>
+        <v>-0.07591740545394288</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.8108776482332729</v>
+        <v>-0.9155743880318852</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.8674051580667381</v>
+        <v>-0.9150698939099939</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-1.942004191891954</v>
+        <v>-2.035837371650921</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.572236372995384</v>
+        <v>-1.672199347797189</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.113268564109816</v>
+        <v>-1.272714625718613</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.9647024428571243</v>
+        <v>-1.185837323887739</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.523909145817498</v>
+        <v>-1.741656239674256</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-2.32307083727671</v>
+        <v>-2.589083667742806</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-2.620390488664526</v>
+        <v>-2.941901573292981</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-2.271627420534898</v>
+        <v>-2.571273079779367</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.001627</t>
+          <t>X &lt; -0.001449</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1454</v>
+        <v>1466</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8108410475759413</v>
+        <v>-0.7183606416550674</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.7496737470633903</v>
+        <v>-0.7103389777018307</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-1.108033917909538</v>
+        <v>-1.135638949813192</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-0.05336967624026556</v>
+        <v>-0.08885017421602726</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.41783607233765</v>
+        <v>-0.5413072523320679</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.2883983615496817</v>
+        <v>-0.3673649596014954</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.9519525500241457</v>
+        <v>-1.070107782350604</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.8342743981276826</v>
+        <v>-0.9560735897542258</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.2411680909814038</v>
+        <v>-0.3444098822770627</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3869440845383991</v>
+        <v>0.2295796716397547</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3967226276485718</v>
+        <v>-0.5489716157939029</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.4613360808051041</v>
+        <v>-0.6572789483536781</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.3620579095348546</v>
+        <v>-0.6056409708407173</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.3039366611007495</v>
+        <v>-0.5913189006502293</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; 0.03813</t>
+          <t>X &lt; 0.03829</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1635</v>
+        <v>1646</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.145964574223669</v>
+        <v>-1.093595851408992</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.511652821837401</v>
+        <v>-1.499802782177937</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.509959778098057</v>
+        <v>-1.499700404694295</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.4964659939441916</v>
+        <v>-0.4924085576259571</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.6978576258897533</v>
+        <v>-0.7678421491521803</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.6109540282132997</v>
+        <v>-0.6437394901585591</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.9672925178935827</v>
+        <v>-1.034746537043361</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.9141204659279794</v>
+        <v>-0.9838725685941014</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.14934943804505</v>
+        <v>-0.2612351094327181</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.2545822693528237</v>
+        <v>0.0997095417696201</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.09888883633503553</v>
+        <v>-0.2523626182827741</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.03088702901116136</v>
+        <v>-0.1602682872600596</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.1952480668218612</v>
+        <v>-0.03572578762974388</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.5780760508527791</v>
+        <v>0.308377581292028</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; 0.07788</t>
+          <t>X &lt; 0.07803</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1876</v>
+        <v>1889</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.8663051252934864</v>
+        <v>-0.7750960520163233</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-1.284898733767676</v>
+        <v>-1.278980651231684</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.174737843276375</v>
+        <v>-1.223869003620699</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.1678890858677207</v>
+        <v>-0.1180696607236982</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.4121792971709013</v>
+        <v>-0.5260548010452553</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.5635936122169767</v>
+        <v>-0.6463529210259864</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.9382487562542465</v>
+        <v>-1.047764678205951</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.21735564366945</v>
+        <v>-1.327008257644543</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6648705023466093</v>
+        <v>-0.8076064807880883</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2091800143437794</v>
+        <v>-0.387732229348849</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6502563382081235</v>
+        <v>-0.8267705815945163</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6395125369368344</v>
+        <v>-0.7922218947929309</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.4972813687728319</v>
+        <v>-0.6819223354656359</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.3482229912890631</v>
+        <v>-0.562141578362862</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; 0.1176</t>
+          <t>X &lt; 0.1178</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2226</v>
+        <v>2237</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4487588174928092</v>
+        <v>-0.4212229359981023</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.366454223687548</v>
+        <v>-1.358740221736923</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.8436012687465961</v>
+        <v>-0.8393400656173284</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.3316036420457209</v>
+        <v>-0.3295505117935136</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.4430363518650253</v>
+        <v>-0.4830794424402853</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5241529661126663</v>
+        <v>-0.5424260783849846</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6742133428789998</v>
+        <v>-0.7126939410503326</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.072281959378728</v>
+        <v>-1.109903621350107</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.3470350433188614</v>
+        <v>-0.4091464393595388</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.006432184938191199</v>
+        <v>-0.09298040995646772</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.5000279992507757</v>
+        <v>-0.5846798235153869</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.2162041929443106</v>
+        <v>-0.3230381611201807</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.1072526603687152</v>
+        <v>-0.02302904922650839</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.4034096809293573</v>
+        <v>0.2512634654962085</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; 0.1574</t>
+          <t>X &lt; 0.1575</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2488</v>
+        <v>2500</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3817556946686977</v>
+        <v>-0.3811822586315188</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.8121021235981729</v>
+        <v>-0.8289576998517489</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-0.0651048008702233</v>
+        <v>-0.08638970202142104</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2470345815922315</v>
+        <v>0.2245304496300449</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.2111894349628329</v>
+        <v>0.1556008277322363</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.04987200921042501</v>
+        <v>0.01172047447214908</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.3077057124282092</v>
+        <v>0.2520557402342263</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.2175064839006637</v>
+        <v>-0.2716835172326242</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.3853428222349535</v>
+        <v>0.3120338583857318</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.8418428332365693</v>
+        <v>0.7483686568824126</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.2585395419684886</v>
+        <v>0.1673641522850886</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3959391740605156</v>
+        <v>0.2880138637181844</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.8824281383542072</v>
+        <v>0.7550690055640885</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>1.050902191250231</v>
+        <v>0.9070167064439048</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; 0.1971</t>
+          <t>X &lt; 0.1972</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2663</v>
+        <v>2674</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.3882403952578244</v>
+        <v>-0.370178814094281</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.8210740862150061</v>
+        <v>-0.8170417022989795</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.3357889907765568</v>
+        <v>-0.334326712137802</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.1853053045329105</v>
+        <v>-0.1842665531190164</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.2542193549863043</v>
+        <v>-0.2806074285830391</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.2733407508237491</v>
+        <v>-0.2857615874041102</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.0006263074167236482</v>
+        <v>-0.02777245287282426</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.297338395212428</v>
+        <v>-0.3239759258995747</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1494950421538732</v>
+        <v>0.1074262762376037</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.6326695416957619</v>
+        <v>0.5738308896773816</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.03663039145725833</v>
+        <v>-0.02009860253239992</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.2797520993074656</v>
+        <v>0.2085258845947564</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.6315645789329949</v>
+        <v>0.5447008163911562</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6910524943800596</v>
+        <v>0.5906965867729994</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; 0.2369</t>
+          <t>X &lt; 0.237</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2846</v>
+        <v>2857</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1899051875822764</v>
+        <v>-0.1756170513678157</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5231728023945408</v>
+        <v>-0.5206155046751135</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.01085137789109325</v>
+        <v>0.0108810514332518</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.0901303467197323</v>
+        <v>0.09001445014698817</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.02625297530932613</v>
+        <v>0.003573110069908125</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.1827075462492971</v>
+        <v>-0.1931527270943505</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.1081417553780639</v>
+        <v>-0.1300726243672372</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.4508856682769675</v>
+        <v>-0.4720827546618196</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.03670175772749218</v>
+        <v>-0.07068079616261258</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.3958965067461833</v>
+        <v>0.3480863542848454</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.1408114033651984</v>
+        <v>0.09370429236873434</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3003320263686149</v>
+        <v>0.2415033281801939</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.6025313307216678</v>
+        <v>0.5308619773886534</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.8132470403417571</v>
+        <v>0.729865848901035</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.2766</t>
+          <t>X &lt; 0.2767</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3057</v>
+        <v>3068</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1575204515503401</v>
+        <v>0.1675902199036656</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.03540613141831983</v>
+        <v>-0.03484735160127883</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.6304667784785991</v>
+        <v>0.628270276049733</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.713452711205143</v>
+        <v>0.7110832637148405</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.6823614950552965</v>
+        <v>0.6622202865980995</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.606351283063276</v>
+        <v>0.5954442359387073</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7028432459809437</v>
+        <v>0.682810602230397</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.5150384342195053</v>
+        <v>0.4952202208876244</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.8314776955038781</v>
+        <v>0.801754060026056</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.077946289812147</v>
+        <v>1.037801397830229</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.8265582655826549</v>
+        <v>0.7870958893747897</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.010361557940591</v>
+        <v>0.9615336797871521</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.328353585074524</v>
+        <v>1.269232841495992</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>1.736614283154644</v>
+        <v>1.667486067591241</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.3164</t>
+          <t>X &lt; 0.3165</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3240</v>
+        <v>3251</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2214632177461553</v>
+        <v>-0.2123177072399258</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.3098143007199567</v>
+        <v>-0.3084283522739142</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.2347506073034964</v>
+        <v>0.2340031445609085</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.258736250619755</v>
+        <v>0.2580058702413695</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.1066010171963825</v>
+        <v>0.09225830865369034</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.1438154221193599</v>
+        <v>0.1364272734090193</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1683571045256116</v>
+        <v>0.1539510594913196</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.09697074093948999</v>
+        <v>-0.1108414142392817</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.2596287272373701</v>
+        <v>0.2376249366714234</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4440718155483978</v>
+        <v>0.4139114688747796</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.3184654200571515</v>
+        <v>0.2885586083047897</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3702968143688068</v>
+        <v>0.3333388088036173</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6772674864069614</v>
+        <v>0.6320431851419528</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.9206969592229228</v>
+        <v>0.8679025877112139</v>
       </c>
     </row>
     <row r="23">
@@ -4792,49 +4792,49 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3375</v>
+        <v>3386</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1491568805933809</v>
+        <v>-0.1417681944074332</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.4753321206457173</v>
+        <v>-0.4735125710198886</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.1454677198121672</v>
+        <v>-0.1449603690669861</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.000811014851102243</v>
+        <v>0.0009254585226230461</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.1963563575768674</v>
+        <v>-0.2072167403628242</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2966475417873866</v>
+        <v>-0.3013613407961842</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.3948703444756703</v>
+        <v>-0.4049669598953614</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5796889427424361</v>
+        <v>-0.5894821213374897</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.417425639517127</v>
+        <v>-0.4334406894222198</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.215319310245242</v>
+        <v>-0.2381826545296519</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3442818881224028</v>
+        <v>-0.3668664145873421</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.2045082181140501</v>
+        <v>-0.2331984462449412</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.07321594593981473</v>
+        <v>0.03768250282831076</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.2861290579883544</v>
+        <v>0.2443587028999019</v>
       </c>
     </row>
     <row r="24">
@@ -4844,49 +4844,49 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3431</v>
+        <v>3442</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.2451436728107765</v>
+        <v>-0.2380423603428454</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.6212917837782541</v>
+        <v>-0.6190561364470071</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.2742064543148643</v>
+        <v>-0.2732997046129739</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.1572877137913125</v>
+        <v>-0.1566793577222327</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3019146620465989</v>
+        <v>-0.3114745828528243</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.4829956997985931</v>
+        <v>-0.4866499575367271</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.5228792504002939</v>
+        <v>-0.5316241225749607</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.6250484484503218</v>
+        <v>-0.6337380202999654</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.4664368056591215</v>
+        <v>-0.4808451355845449</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2814956636361003</v>
+        <v>-0.3021617538915748</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.4117126203294674</v>
+        <v>-0.4320906673884934</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.244548790030052</v>
+        <v>-0.2706332952097199</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.007361059992639696</v>
+        <v>-0.03964070276867204</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.1474458104738616</v>
+        <v>0.1095966018535535</v>
       </c>
     </row>
     <row r="25">
@@ -4896,49 +4896,49 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3471</v>
+        <v>3482</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.270812701028035</v>
+        <v>-0.2640460165894112</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.5750191491508616</v>
+        <v>-0.57296836052938</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.322600102264758</v>
+        <v>-0.321553093605182</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3491792466953427</v>
+        <v>-0.3479790541646253</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.4121792971709013</v>
+        <v>-0.4207259998134916</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.5877909649716599</v>
+        <v>-0.5907984563532196</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.6282201934375777</v>
+        <v>-0.6359822589570356</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7346175533433765</v>
+        <v>-0.7422971637470397</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.6361018026918259</v>
+        <v>-0.6489692858849452</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.4343445635554701</v>
+        <v>-0.4531512520550223</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.5078926132144588</v>
+        <v>-0.5265864642204434</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3134922747407458</v>
+        <v>-0.3376394597768595</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1126992701695571</v>
+        <v>-0.1425679201422341</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.07170478064273311</v>
+        <v>0.03650550598440816</v>
       </c>
     </row>
     <row r="26">
@@ -4948,49 +4948,49 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3511</v>
+        <v>3522</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2107684709429805</v>
+        <v>-0.204595558974674</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.529797269780417</v>
+        <v>-0.5279238845759409</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.3131086020499865</v>
+        <v>-0.3121047358893918</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.3379036899565619</v>
+        <v>-0.3367578061802305</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4347106451332863</v>
+        <v>-0.4425403979814959</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.5765351868898634</v>
+        <v>-0.5792722016554563</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6458899382250038</v>
+        <v>-0.6529647504225338</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.6995277078834405</v>
+        <v>-0.7066712926034739</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.5743751046839662</v>
+        <v>-0.5864583548062612</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4414671727227528</v>
+        <v>-0.4589112664257655</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.5165101702910349</v>
+        <v>-0.5338312926136624</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.3239343422078065</v>
+        <v>-0.3463707965445266</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.1586903684973535</v>
+        <v>-0.186388076093742</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.002310449590993358</v>
+        <v>-0.03492537192065726</v>
       </c>
     </row>
     <row r="27">
@@ -5000,49 +5000,49 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3572</v>
+        <v>3583</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.04019078646182805</v>
+        <v>-0.03513963356329697</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.213753909312473</v>
+        <v>-0.212899480279269</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.03529661747965207</v>
+        <v>-0.03516268021619595</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.05737421624447592</v>
+        <v>-0.05711502524751211</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.1336980407312538</v>
+        <v>-0.1414922208119265</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2679549496779714</v>
+        <v>-0.2711837558005001</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.3095444346947644</v>
+        <v>-0.3167138219832069</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.3701366307976528</v>
+        <v>-0.3773313277701362</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2201097836132817</v>
+        <v>-0.2318282501730664</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1038680052048306</v>
+        <v>-0.1203612525972346</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1810289184751142</v>
+        <v>-0.1973849864506079</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.09288026803911009</v>
+        <v>0.07165138884452915</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.3042221231270616</v>
+        <v>0.2781057729999716</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.4899115638985236</v>
+        <v>0.4592690089836751</v>
       </c>
     </row>
     <row r="28">
@@ -5052,101 +5052,101 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3623</v>
+        <v>3634</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.0768397450432019</v>
+        <v>0.08105900044891712</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.08935109196131918</v>
+        <v>-0.08890053922549868</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.1636493314926852</v>
+        <v>0.1631788629593274</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.1988154392538632</v>
+        <v>0.198290732319272</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1436083376460502</v>
+        <v>0.135765564353747</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.01549036680069804</v>
+        <v>0.01178616212996531</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.08172328330429934</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.09285350026156891</v>
+        <v>-0.1000953288846489</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.02672015616797552</v>
+        <v>0.01544648901894874</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1018736083090204</v>
+        <v>0.08638220573750743</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.05055417025082676</v>
+        <v>0.03512800475752442</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.403915908584807</v>
+        <v>0.383778835898859</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.5512690516175951</v>
+        <v>0.526857676615613</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.7099889653702078</v>
+        <v>0.6815241362732891</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.5947</t>
+          <t>X &lt; 0.5946</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3663</v>
+        <v>3674</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.2938391381272396</v>
+        <v>0.2970484680340917</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1119795090548763</v>
+        <v>0.1118114697726824</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.3852005253974653</v>
+        <v>0.3840721518459915</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3670107694578419</v>
+        <v>0.3659841786877607</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.2793540211372658</v>
+        <v>0.2717182381256933</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1831498137630945</v>
+        <v>0.1792452317507625</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.08611812308057409</v>
+        <v>0.07913053119985847</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.09731832431170062</v>
+        <v>0.09012206241969523</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.1877120296252386</v>
+        <v>0.1768760685020538</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.2255483565780168</v>
+        <v>0.2109359988362129</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.1453114078652078</v>
+        <v>0.1308564249791218</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4679324678358867</v>
+        <v>0.4491689440065159</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.5818150477424169</v>
+        <v>0.5591963342244526</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.7139750858343845</v>
+        <v>0.6876808327367812</v>
       </c>
     </row>
     <row r="30">
@@ -5156,101 +5156,101 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3723</v>
+        <v>3734</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.4098762606862039</v>
+        <v>0.4122260454092483</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.2854079165624555</v>
+        <v>0.2847142933741438</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.4943798392632814</v>
+        <v>0.4929463993727694</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.5053928889185144</v>
+        <v>0.5039682539682531</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.3837330360515594</v>
+        <v>0.3766910903369549</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.2938861251757672</v>
+        <v>0.2901027671164513</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.2507016238220388</v>
+        <v>0.2441121976040037</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.2274337244363025</v>
+        <v>0.2207602860886055</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.3422500594949938</v>
+        <v>0.3323089007054847</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.3658361129390215</v>
+        <v>0.3526401317788697</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.2836325606791092</v>
+        <v>0.2706065979839067</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.5211110023131127</v>
+        <v>0.5044788073949391</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.6801093643198897</v>
+        <v>0.6599531027953418</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.7332236949298974</v>
+        <v>0.7100590203164359</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.6742</t>
+          <t>X &lt; 0.6741</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3798</v>
+        <v>3809</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.129947259940586</v>
+        <v>0.1324836748513718</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.1336196611787202</v>
+        <v>0.1333533302084078</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3044102931694823</v>
+        <v>0.3035490178728253</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.3965028957393457</v>
+        <v>0.3954101672090644</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.371676214001802</v>
+        <v>0.3657609615699684</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.2369079982695439</v>
+        <v>0.2338339189426435</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.2191712189998256</v>
+        <v>0.2137458172429234</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.1608568984166823</v>
+        <v>0.1554747890707873</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.2721887570897294</v>
+        <v>0.2640857064462949</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.2785252247800898</v>
+        <v>0.2677948003348192</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.19388162218128</v>
+        <v>0.1833365908153013</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.3746963078588621</v>
+        <v>0.3612483750332984</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.5222225440842507</v>
+        <v>0.5058458601765707</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.6050337446655618</v>
+        <v>0.5860820779324953</v>
       </c>
     </row>
     <row r="32">
@@ -5260,205 +5260,205 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3835</v>
+        <v>3846</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.0918490422307201</v>
+        <v>0.09418980766030671</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.0279914558143517</v>
+        <v>0.02801746631797641</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.03730745888547204</v>
+        <v>0.03721474022166404</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.1296975390062656</v>
+        <v>0.1293716656787112</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.1258737366659801</v>
+        <v>0.1211825803747431</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.0472448549439406</v>
+        <v>0.04497162139876565</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.002785617162196274</v>
+        <v>-0.001508870084499847</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.08555741874517508</v>
+        <v>-0.08971111289296374</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.05009161886551539</v>
+        <v>0.04340466649685482</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.003979191877810706</v>
+        <v>-0.01284457078448753</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0116880977533711</v>
+        <v>-0.02058386167000492</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.1676609320855675</v>
+        <v>0.1561235339861327</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3357265093723001</v>
+        <v>0.3214706746858909</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.4198680120662885</v>
+        <v>0.4032829570939285</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.7537</t>
+          <t>X &lt; 0.7536</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3852</v>
+        <v>3863</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.145215922893847</v>
+        <v>0.1472669160830904</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.1004444602527528</v>
+        <v>0.100259477053946</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.0821143249369598</v>
+        <v>0.08189411351648346</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2005758713822132</v>
+        <v>0.2000479510161881</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2203171973945572</v>
+        <v>0.2155914729796038</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.117462018510281</v>
+        <v>0.1151044481330814</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.07284365870168585</v>
+        <v>0.06857980875967229</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.04307021113321952</v>
+        <v>-0.04711006137366525</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.06579629002617082</v>
+        <v>0.05941603302301246</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.008220886159449492</v>
+        <v>-0.0002034751333113149</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>0.02558677452189784</v>
+        <v>0.01706339575888194</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.2043060093310132</v>
+        <v>0.193259137098444</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.3697858004140144</v>
+        <v>0.3561498982587707</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.4805215813528392</v>
+        <v>0.4645937191283451</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.7934</t>
+          <t>X &lt; 0.7933</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3869</v>
+        <v>3880</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.120835643860282</v>
+        <v>0.1228190767313109</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.1464961758091903</v>
+        <v>0.1461766603579875</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.1523017493787364</v>
+        <v>0.1518834074764328</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2966127850160163</v>
+        <v>0.2958134410576534</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3139326339702819</v>
+        <v>0.3091749857056811</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2128565399406384</v>
+        <v>0.2103441380080966</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.193886743220439</v>
+        <v>0.1895089776782655</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.07646356033453117</v>
+        <v>0.07231846421878885</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.2104286951002479</v>
+        <v>0.2039874030338922</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.1494127528222506</v>
+        <v>0.1410602267866352</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1400136752947461</v>
+        <v>0.1316408600503465</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.2664623413875304</v>
+        <v>0.2558294103535275</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.4035458625421882</v>
+        <v>0.390525310030192</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.4889491952618457</v>
+        <v>0.4738208301552476</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.8332</t>
+          <t>X &lt; 0.8331</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3900</v>
+        <v>3910</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.2152250376997387</v>
+        <v>0.2046472880367958</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.2535011483854603</v>
+        <v>0.24123429240489</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.2561589641601998</v>
+        <v>0.2439090873603931</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.3748094357466485</v>
+        <v>0.3622448979591866</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.4389070552783565</v>
+        <v>0.4228093287743206</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.3922006972402485</v>
+        <v>0.3778993910661583</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.3215650153698988</v>
+        <v>0.3057425374471165</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.2270011947431314</v>
+        <v>0.2114470613094213</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.359457282544561</v>
+        <v>0.3418592650436807</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.2666004181640744</v>
+        <v>0.2475858521395509</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.2813014746777185</v>
+        <v>0.2622566702234366</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.3814269992721719</v>
+        <v>0.3604099345915515</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.4884773748357958</v>
+        <v>0.4654993310048567</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.5237358955952018</v>
+        <v>0.4989348650116767</v>
       </c>
     </row>
   </sheetData>
